--- a/INPUT/Rentabilidad por FP 2026.xlsx
+++ b/INPUT/Rentabilidad por FP 2026.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xitanium\Documents\rodri\xio\xio\Veritrade_Dashboard\INPUT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7AB47D-0878-4271-9979-40E5623F94F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C55B05-A39E-48C4-B0ED-6BC9DA5CC6D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{D0C09B95-B007-4212-AB74-70908523E143}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{D0C09B95-B007-4212-AB74-70908523E143}"/>
   </bookViews>
   <sheets>
     <sheet name="TD" sheetId="3" r:id="rId1"/>
     <sheet name="Resumen" sheetId="1" r:id="rId2"/>
     <sheet name="Detalle Costos" sheetId="2" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Detalle Costos'!$A$4:$U$158</definedName>
@@ -23,7 +24,8 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="455">
   <si>
     <t>ANÁLISIS DE RENTABILIDAD</t>
   </si>
@@ -2237,6 +2239,9 @@
       <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="5" tint="0.59999389629810485"/>
@@ -2309,9 +2314,6 @@
       <font>
         <b/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -2521,6 +2523,201 @@
     </cacheField>
     <cacheField name="EBITDA" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-189035.0996326131" maxValue="203282.1727407841"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Xitanium" refreshedDate="46111.199293750004" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="66" xr:uid="{7D31180D-F559-498B-BEB5-32CD8E42C358}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="B3:AY69" sheet="Resumen"/>
+  </cacheSource>
+  <cacheFields count="50">
+    <cacheField name="MES LINK" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="MES _x000a_EJERCICIO" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="FP" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Emision" numFmtId="16">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="1900-01-14T00:00:00" maxDate="2026-02-28T00:00:00"/>
+    </cacheField>
+    <cacheField name="Fecha Embarque" numFmtId="16">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-09T00:00:00" maxDate="2026-03-28T00:00:00"/>
+    </cacheField>
+    <cacheField name=" Cantidad " numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="351"/>
+    </cacheField>
+    <cacheField name="Producto" numFmtId="0">
+      <sharedItems count="11">
+        <s v="POTA REPRODUCTORES"/>
+        <s v="POTA NUCAS"/>
+        <s v="POTA REJOS CONGELADOS"/>
+        <s v="POTA CONOS"/>
+        <s v="POTA FILETE CONGELADO"/>
+        <s v="POTA ALAS CONGELADAS"/>
+        <s v="RESIDUOS DE POTA"/>
+        <s v="POTA MEMBRANA PRECOCIDA"/>
+        <s v="POTA  TELILLA PRECOCIDA"/>
+        <s v="POTA FILETE PRECOCIDO"/>
+        <s v="POTA ALAS COCIDAS"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Corte" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Espec." numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="País" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Puerto " numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Cliente (Razón Social)" numFmtId="0">
+      <sharedItems count="17">
+        <s v="OCEANUS FISH"/>
+        <s v="DAIRECK S.A."/>
+        <s v="TSUJINO"/>
+        <s v="GLOBAL OCEAN"/>
+        <s v="PROVEEDORA DE PRODUCTOS MARINOS"/>
+        <s v="FOOD &amp; BEVERAGES TRADERS"/>
+        <s v="OVERSEA"/>
+        <s v="Hunan Jinyueyang "/>
+        <s v="Longkou Yunfeng Aquatic"/>
+        <s v="AVANCE GROUP"/>
+        <s v="SACRAMENTO CO., LTD"/>
+        <s v="KULALIA"/>
+        <s v="Pesciro Asia International LTD."/>
+        <s v="Pesciro SL"/>
+        <s v="SHANDONG SHEENIER"/>
+        <s v="LONGKOU JIABAO AQUATIC"/>
+        <s v="LONGKOU BOHAI"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Contacto " numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Precio TM" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="3400"/>
+    </cacheField>
+    <cacheField name="VALOR _x000a_CFR" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4350" maxValue="669600"/>
+    </cacheField>
+    <cacheField name=" FOB / TM " numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="3292.5925925925926"/>
+    </cacheField>
+    <cacheField name="Costo Flete" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="40339"/>
+    </cacheField>
+    <cacheField name="VALOR _x000a_FOB" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4350" maxValue="646400"/>
+    </cacheField>
+    <cacheField name="Cantidad de FCL (Contenedores)" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="13"/>
+    </cacheField>
+    <cacheField name="M/V Nave" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Booking" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="11400418" maxValue="6447908790"/>
+    </cacheField>
+    <cacheField name=" Naviera " numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Puerto" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="CÓDIGO" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="10005721" maxValue="10009332"/>
+    </cacheField>
+    <cacheField name="Categoría" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="MATCH" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="COSTO _x000a_UNITARIO" numFmtId="43">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="2114.7381481481502"/>
+    </cacheField>
+    <cacheField name="Materia Prima" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="370785.71870256303"/>
+    </cacheField>
+    <cacheField name="MOD" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="151457.49655569636"/>
+    </cacheField>
+    <cacheField name="Envases" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6516.3554632679306"/>
+    </cacheField>
+    <cacheField name="CIF" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="111218.93164828864"/>
+    </cacheField>
+    <cacheField name="COSTO _x000a_VENTAS" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="611014.73302305548"/>
+    </cacheField>
+    <cacheField name="Cant" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="3" maxValue="351"/>
+    </cacheField>
+    <cacheField name="C.U" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1397.2773083886541" maxValue="2114.7381481481502"/>
+    </cacheField>
+    <cacheField name="Cotos Vta" numFmtId="165">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="5803.9692134831503" maxValue="611014.73302305548"/>
+    </cacheField>
+    <cacheField name="UTILIDAD _x000a_BRUTA" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-154714.73302305548" maxValue="213840"/>
+    </cacheField>
+    <cacheField name="MARGEN _x000a_BRUTO" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.69090909090909092" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Flete" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="40339"/>
+    </cacheField>
+    <cacheField name="SS Logístico" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="20250"/>
+    </cacheField>
+    <cacheField name="GASTO_x000a_VENTAS" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="60589"/>
+    </cacheField>
+    <cacheField name="GASTO _x000a_ADM" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="17439.677419354837"/>
+    </cacheField>
+    <cacheField name="DRAWBACK" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="19392"/>
+    </cacheField>
+    <cacheField name="UTILIDAD _x000a_OPERATIVA" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-215701.55306833482" maxValue="189931.17684529905"/>
+    </cacheField>
+    <cacheField name="MARGEN _x000a_OPERATIVO" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.88256874223358972" maxValue="1"/>
+    </cacheField>
+    <cacheField name="GASTO _x000a_FINANCIERO" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="38105.129032258068"/>
+    </cacheField>
+    <cacheField name="UTILIDAD _x000a_NETA" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-247594.594737551" maxValue="178504.68386301855"/>
+    </cacheField>
+    <cacheField name="MARGEN _x000a_NETO" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-1.0021710019679986" maxValue="1"/>
+    </cacheField>
+    <cacheField name="DEPRECIACIÓN" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="35863.548387096773"/>
+    </cacheField>
+    <cacheField name="EBITDA" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-189035.0996326131" maxValue="203282.1727407841"/>
+    </cacheField>
+    <cacheField name="MARGEN _x000a_EBITDA" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.82637768206740692" maxValue="1"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -5902,8 +6099,3445 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="66">
+  <r>
+    <s v="ENERO"/>
+    <s v="ENERO"/>
+    <s v="127-2025"/>
+    <d v="1900-11-20T00:00:00"/>
+    <d v="2026-01-11T00:00:00"/>
+    <n v="26"/>
+    <x v="0"/>
+    <s v="Rejos"/>
+    <m/>
+    <s v="España"/>
+    <s v="Valencia"/>
+    <x v="0"/>
+    <s v="Ignacio / Ives"/>
+    <n v="2848.6153846153848"/>
+    <n v="74064"/>
+    <n v="2670.3846153846152"/>
+    <n v="4634"/>
+    <n v="69430"/>
+    <n v="1"/>
+    <s v="MERSIN EXPRESS 603N"/>
+    <n v="26106924"/>
+    <s v="HAPAG"/>
+    <s v="PAITA"/>
+    <n v="10007567"/>
+    <s v="Compensación"/>
+    <s v="ENERO10007567Compensación"/>
+    <n v="1830"/>
+    <n v="31604.018542872498"/>
+    <n v="7767.6489739716217"/>
+    <n v="466.19181744573058"/>
+    <n v="7742.1406657101552"/>
+    <n v="47580"/>
+    <n v="22.658000000000001"/>
+    <n v="1829.8234619119073"/>
+    <n v="41460.14"/>
+    <n v="26484"/>
+    <n v="0.35758263123784834"/>
+    <n v="4634"/>
+    <n v="1500"/>
+    <n v="6134"/>
+    <n v="6297.6612903225805"/>
+    <n v="2082.9"/>
+    <n v="16135.23870967742"/>
+    <n v="0.21785535090836872"/>
+    <n v="13760.185483870968"/>
+    <n v="2375.0532258064522"/>
+    <n v="3.206757973923164E-2"/>
+    <n v="12950.725806451614"/>
+    <n v="29085.964516129032"/>
+    <n v="0.39271393006223038"/>
+  </r>
+  <r>
+    <s v="ENERO"/>
+    <s v="ENERO"/>
+    <s v="128-2025B"/>
+    <d v="1900-11-20T00:00:00"/>
+    <d v="2026-01-31T00:00:00"/>
+    <n v="17.04"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="1000-up"/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="1"/>
+    <s v="Julieta"/>
+    <n v="1850"/>
+    <n v="31524"/>
+    <n v="1656.3380281690143"/>
+    <n v="2343"/>
+    <n v="28224"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26005S"/>
+    <n v="6443191850"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Compensación"/>
+    <s v="ENERO10005779Compensación"/>
+    <n v="1930"/>
+    <n v="20697.484505029512"/>
+    <n v="6988.7487369194496"/>
+    <n v="251.1516477056781"/>
+    <n v="4949.8151103453556"/>
+    <n v="32887.199999999997"/>
+    <n v="17.04"/>
+    <n v="1977.4951253481865"/>
+    <n v="33696.516935933098"/>
+    <n v="-1363.1999999999971"/>
+    <n v="-4.3243243243243148E-2"/>
+    <n v="2343"/>
+    <n v="983.07692307692309"/>
+    <n v="3326.0769230769229"/>
+    <n v="4127.3903225806453"/>
+    <n v="846.71999999999991"/>
+    <n v="-7969.947245657565"/>
+    <n v="-0.25282157231498431"/>
+    <n v="9018.213870967742"/>
+    <n v="-16988.161116625306"/>
+    <n v="-0.53889611459920395"/>
+    <n v="8487.706451612903"/>
+    <n v="517.75920595533808"/>
+    <n v="1.6424286447003493E-2"/>
+  </r>
+  <r>
+    <s v="ENERO"/>
+    <s v="ENERO"/>
+    <s v="128-2025B"/>
+    <d v="1900-11-20T00:00:00"/>
+    <d v="2026-01-31T00:00:00"/>
+    <n v="3"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="500 - 1 kg."/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="1"/>
+    <s v="Julieta"/>
+    <n v="1450"/>
+    <n v="4350"/>
+    <n v="1450"/>
+    <n v="412.5"/>
+    <n v="4350"/>
+    <n v="0"/>
+    <m/>
+    <n v="6443191850"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10005781"/>
+    <s v="Compensación"/>
+    <s v="ENERO10005781Compensación"/>
+    <n v="1980"/>
+    <n v="3757.0131752477705"/>
+    <n v="1227.8049305981747"/>
+    <n v="49.950511210059688"/>
+    <n v="905.2313829439945"/>
+    <n v="5940"/>
+    <n v="3"/>
+    <n v="1934.6564044943834"/>
+    <n v="5803.9692134831503"/>
+    <n v="-1590"/>
+    <n v="-0.36551724137931035"/>
+    <n v="412.5"/>
+    <n v="173.07692307692309"/>
+    <n v="585.57692307692309"/>
+    <n v="726.65322580645159"/>
+    <n v="130.5"/>
+    <n v="-2771.7301488833746"/>
+    <n v="-0.63717934457089076"/>
+    <n v="1587.7137096774195"/>
+    <n v="-4359.4438585607941"/>
+    <n v="-1.0021710019679986"/>
+    <n v="1494.3145161290322"/>
+    <n v="-1277.4156327543424"/>
+    <n v="-0.29365876615042352"/>
+  </r>
+  <r>
+    <s v="ENERO"/>
+    <s v="ENERO"/>
+    <s v="128-2025B"/>
+    <d v="1900-11-20T00:00:00"/>
+    <d v="2026-01-31T00:00:00"/>
+    <n v="3.96"/>
+    <x v="2"/>
+    <s v="Rejos"/>
+    <s v="1 - 2 kgs."/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="1"/>
+    <s v="Julieta"/>
+    <n v="2234.3434343434342"/>
+    <n v="8848"/>
+    <n v="2800"/>
+    <n v="544.5"/>
+    <n v="8303.5"/>
+    <n v="0"/>
+    <m/>
+    <n v="6443191850"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10007162"/>
+    <s v="Compensación"/>
+    <s v="ENERO10007162Compensación"/>
+    <n v="1790"/>
+    <n v="4604.3695814081602"/>
+    <n v="1214.8181219670928"/>
+    <n v="61.899522527468079"/>
+    <n v="1207.3127740972786"/>
+    <n v="7088.4"/>
+    <n v="3.16"/>
+    <n v="1842.6970447733067"/>
+    <n v="5822.9226614836498"/>
+    <n v="1759.6000000000004"/>
+    <n v="0.198869801084991"/>
+    <n v="544.5"/>
+    <n v="228.46153846153845"/>
+    <n v="772.96153846153845"/>
+    <n v="959.18225806451608"/>
+    <n v="249.10499999999999"/>
+    <n v="276.56120347394585"/>
+    <n v="3.1256917209984837E-2"/>
+    <n v="2095.7820967741936"/>
+    <n v="-1819.2208933002478"/>
+    <n v="-0.20560814797697194"/>
+    <n v="1972.4951612903226"/>
+    <n v="2249.0563647642684"/>
+    <n v="0.25418810632507555"/>
+  </r>
+  <r>
+    <s v="ENERO"/>
+    <s v="ENERO"/>
+    <s v="129-2025"/>
+    <d v="2025-11-21T00:00:00"/>
+    <d v="2026-01-09T00:00:00"/>
+    <n v="24"/>
+    <x v="3"/>
+    <s v="Conos"/>
+    <m/>
+    <s v="Tailandia"/>
+    <s v="Bangkok"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="2100"/>
+    <n v="50400"/>
+    <n v="1962.5"/>
+    <n v="3300"/>
+    <n v="47100"/>
+    <n v="1"/>
+    <s v="ECO MARIN 26002S"/>
+    <n v="6440924270"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10007969"/>
+    <s v="Compensación"/>
+    <s v="ENERO10007969Compensación"/>
+    <n v="1640"/>
+    <n v="30431.61897971667"/>
+    <n v="5331.8120500864879"/>
+    <n v="403.53076527325976"/>
+    <n v="3193.03820492358"/>
+    <n v="39360"/>
+    <n v="24"/>
+    <n v="1644.316650390625"/>
+    <n v="39463.599609375"/>
+    <n v="11040"/>
+    <n v="0.21904761904761905"/>
+    <n v="3300"/>
+    <n v="1384.6153846153848"/>
+    <n v="4684.6153846153848"/>
+    <n v="5813.2258064516127"/>
+    <n v="1413"/>
+    <n v="1955.1588089330025"/>
+    <n v="3.8792833510575449E-2"/>
+    <n v="12701.709677419356"/>
+    <n v="-10746.550868486353"/>
+    <n v="-0.21322521564457048"/>
+    <n v="11954.516129032258"/>
+    <n v="13909.674937965261"/>
+    <n v="0.27598561384851711"/>
+  </r>
+  <r>
+    <s v="ENERO"/>
+    <s v="ENERO"/>
+    <s v="137-2025"/>
+    <d v="2025-12-09T00:00:00"/>
+    <d v="2026-01-21T00:00:00"/>
+    <n v="24"/>
+    <x v="4"/>
+    <s v="Filete"/>
+    <s v="2 - 4 kg"/>
+    <s v="Taiwan"/>
+    <s v="KAOHSIUNG"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1966.6666666666667"/>
+    <n v="47200"/>
+    <n v="1841.5416666666667"/>
+    <n v="3003"/>
+    <n v="44197"/>
+    <n v="1"/>
+    <s v="ECO MARIN 25052N"/>
+    <s v="LIMF26385300"/>
+    <s v="ONE"/>
+    <s v="PAITA"/>
+    <n v="10005721"/>
+    <s v="Compensación"/>
+    <s v="ENERO10005721Compensación"/>
+    <n v="1860"/>
+    <n v="27074.763257694456"/>
+    <n v="9821.5947948746671"/>
+    <n v="427.38654616783856"/>
+    <n v="7316.2554012630353"/>
+    <n v="44640"/>
+    <n v="23.7"/>
+    <n v="1889.3858510966963"/>
+    <n v="44778.444670991703"/>
+    <n v="2560"/>
+    <n v="5.4237288135593219E-2"/>
+    <n v="3003"/>
+    <n v="1384.6153846153848"/>
+    <n v="4387.6153846153848"/>
+    <n v="5813.2258064516127"/>
+    <n v="1325.9099999999999"/>
+    <n v="-6314.9311910669976"/>
+    <n v="-0.13379091506497875"/>
+    <n v="12701.709677419356"/>
+    <n v="-19016.640868486353"/>
+    <n v="-0.4028949336543719"/>
+    <n v="11954.516129032258"/>
+    <n v="5639.58493796526"/>
+    <n v="0.11948273173655212"/>
+  </r>
+  <r>
+    <s v="ENERO"/>
+    <s v="ENERO"/>
+    <s v="140-2025"/>
+    <d v="1900-12-12T00:00:00"/>
+    <d v="2026-01-16T00:00:00"/>
+    <n v="24"/>
+    <x v="4"/>
+    <s v="Filete"/>
+    <s v="2-4kg"/>
+    <s v="Japón "/>
+    <s v="Sendai"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1983.3333333333333"/>
+    <n v="47600"/>
+    <n v="1845.7083333333333"/>
+    <n v="3303"/>
+    <n v="44297"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26003S"/>
+    <s v="LIMG00358300"/>
+    <s v="ONE"/>
+    <s v="PAITA"/>
+    <n v="10005721"/>
+    <s v="Compensación"/>
+    <s v="ENERO10005721Compensación"/>
+    <n v="1860"/>
+    <n v="27074.763257694456"/>
+    <n v="9821.5947948746671"/>
+    <n v="427.38654616783856"/>
+    <n v="7316.2554012630353"/>
+    <n v="44640"/>
+    <n v="23.7"/>
+    <n v="1889.3858510966963"/>
+    <n v="44778.444670991703"/>
+    <n v="2960"/>
+    <n v="6.2184873949579833E-2"/>
+    <n v="3303"/>
+    <n v="1384.6153846153848"/>
+    <n v="4687.6153846153848"/>
+    <n v="5813.2258064516127"/>
+    <n v="1328.9099999999999"/>
+    <n v="-6211.9311910669976"/>
+    <n v="-0.1305027561148529"/>
+    <n v="12701.709677419356"/>
+    <n v="-18913.640868486353"/>
+    <n v="-0.39734539639677213"/>
+    <n v="11954.516129032258"/>
+    <n v="5742.58493796526"/>
+    <n v="0.12064254071355589"/>
+  </r>
+  <r>
+    <s v="ENERO"/>
+    <s v="ENERO"/>
+    <s v="145-2025"/>
+    <d v="2025-12-29T00:00:00"/>
+    <d v="2026-01-19T00:00:00"/>
+    <n v="54"/>
+    <x v="2"/>
+    <s v="Rejos"/>
+    <s v="500-1 / 1-2"/>
+    <s v="España"/>
+    <s v="Vigo"/>
+    <x v="3"/>
+    <s v="Jorge"/>
+    <n v="2600"/>
+    <n v="140400"/>
+    <n v="2430.962962962963"/>
+    <n v="9128"/>
+    <n v="131272"/>
+    <n v="2"/>
+    <s v="IZMIT EXPRESS 604N"/>
+    <n v="28952064"/>
+    <s v="HAPAG"/>
+    <s v="PAITA"/>
+    <n v="10007162"/>
+    <s v="Compensación"/>
+    <s v="ENERO10007162Compensación"/>
+    <n v="1790"/>
+    <n v="62786.857928293095"/>
+    <n v="16565.701663187629"/>
+    <n v="844.08439810183756"/>
+    <n v="16463.356010417436"/>
+    <n v="96660"/>
+    <n v="54"/>
+    <n v="1842.6970447733056"/>
+    <n v="99505.640417758506"/>
+    <n v="43740"/>
+    <n v="0.31153846153846154"/>
+    <n v="9128"/>
+    <n v="3115.3846153846152"/>
+    <n v="12243.384615384615"/>
+    <n v="13079.758064516129"/>
+    <n v="3938.16"/>
+    <n v="22355.017320099254"/>
+    <n v="0.15922377008617702"/>
+    <n v="28578.846774193549"/>
+    <n v="-6223.8294540942952"/>
+    <n v="-4.4329269616056231E-2"/>
+    <n v="26897.661290322583"/>
+    <n v="49252.678610421834"/>
+    <n v="0.35080255420528372"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="146-2026"/>
+    <d v="2026-01-05T00:00:00"/>
+    <d v="2026-02-06T00:00:00"/>
+    <n v="10"/>
+    <x v="3"/>
+    <s v="Conos"/>
+    <s v="10 cm - up "/>
+    <s v="Tailandia"/>
+    <s v="Lat Krabang"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="2100"/>
+    <n v="21000"/>
+    <n v="2100"/>
+    <n v="1458.3333333333335"/>
+    <n v="21000"/>
+    <n v="1"/>
+    <s v="ECO MARIN 26006S"/>
+    <n v="6444023300"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10007969"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10007969Compensación"/>
+    <n v="1397.2773083886541"/>
+    <n v="11301.83162341581"/>
+    <n v="2127.4652987326494"/>
+    <n v="166.83162341581172"/>
+    <n v="376.64453832227065"/>
+    <n v="13972.773083886541"/>
+    <n v="10"/>
+    <n v="1397.2773083886541"/>
+    <n v="13972.773083886541"/>
+    <n v="7027.2269161134591"/>
+    <n v="0.33462985314825994"/>
+    <n v="1458.3333333333335"/>
+    <n v="576.92307692307691"/>
+    <n v="2035.2564102564104"/>
+    <n v="401.33390442391237"/>
+    <n v="630"/>
+    <n v="5220.6366014331361"/>
+    <n v="0.24860174292538742"/>
+    <n v="908.63366578963473"/>
+    <n v="4312.0029356435016"/>
+    <n v="0.20533347312588102"/>
+    <n v="755.57945297680976"/>
+    <n v="5976.2160544099461"/>
+    <n v="0.28458171687666411"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="146-2026"/>
+    <d v="2026-01-05T00:00:00"/>
+    <d v="2026-02-06T00:00:00"/>
+    <n v="14.85"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="500-up"/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1700"/>
+    <n v="23800"/>
+    <n v="1700"/>
+    <n v="2165.625"/>
+    <n v="23800"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="10005779"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10005779Compensación"/>
+    <n v="1859.71452825612"/>
+    <n v="16810.063133640517"/>
+    <n v="6080.4464952704202"/>
+    <n v="201.45107324763478"/>
+    <n v="4524.8000424448119"/>
+    <n v="27616.760744603384"/>
+    <n v="14.849"/>
+    <n v="1859.71452825612"/>
+    <n v="27614.901030075125"/>
+    <n v="-3816.7607446033835"/>
+    <n v="-0.16036809851274719"/>
+    <n v="2165.625"/>
+    <n v="856.73076923076928"/>
+    <n v="3022.3557692307695"/>
+    <n v="595.98084806950988"/>
+    <n v="714"/>
+    <n v="-6721.0973619036631"/>
+    <n v="-0.28239904881948164"/>
+    <n v="1349.3209936976077"/>
+    <n v="-8070.4183556012704"/>
+    <n v="-0.33909320821854078"/>
+    <n v="1122.0354876705624"/>
+    <n v="-5599.0618742331008"/>
+    <n v="-0.23525470059802944"/>
+  </r>
+  <r>
+    <s v="ENERO"/>
+    <s v="ENERO"/>
+    <s v="147-2026"/>
+    <d v="2026-01-10T00:00:00"/>
+    <d v="2026-01-28T00:00:00"/>
+    <n v="72"/>
+    <x v="5"/>
+    <s v="Alas"/>
+    <s v="1 - 2 kgs."/>
+    <s v="Tailandia "/>
+    <s v="Bangkok"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1887.7083333333333"/>
+    <n v="135915"/>
+    <n v="1754.25"/>
+    <n v="9609"/>
+    <n v="126306"/>
+    <n v="3"/>
+    <s v="ECO MARIN 26004N"/>
+    <s v="LIMG01524600"/>
+    <s v="ONE"/>
+    <s v="PAITA"/>
+    <n v="10006720"/>
+    <s v="Compensación"/>
+    <s v="ENERO10006720Compensación"/>
+    <n v="1720"/>
+    <n v="81764.360643671505"/>
+    <n v="18919.257644210982"/>
+    <n v="1185.8373623695809"/>
+    <n v="21970.544349747925"/>
+    <n v="123840"/>
+    <n v="69.7"/>
+    <n v="1723.9159631619368"/>
+    <n v="120156.942632387"/>
+    <n v="12075"/>
+    <n v="8.8842291137843504E-2"/>
+    <n v="9609"/>
+    <n v="4153.8461538461543"/>
+    <n v="13762.846153846154"/>
+    <n v="17439.677419354837"/>
+    <n v="3789.18"/>
+    <n v="-15338.343573200989"/>
+    <n v="-0.11285247083251289"/>
+    <n v="38105.129032258068"/>
+    <n v="-53443.472605459057"/>
+    <n v="-0.39321246812683702"/>
+    <n v="35863.548387096773"/>
+    <n v="20525.204813895783"/>
+    <n v="0.1510150080115939"/>
+  </r>
+  <r>
+    <s v="ENERO"/>
+    <s v="ENERO"/>
+    <m/>
+    <d v="2026-01-31T00:00:00"/>
+    <d v="2026-01-31T00:00:00"/>
+    <n v="0"/>
+    <x v="6"/>
+    <s v="Residuos"/>
+    <s v="Residuos"/>
+    <s v="Residuos"/>
+    <s v="Residuos"/>
+    <x v="4"/>
+    <m/>
+    <n v="0"/>
+    <n v="24314.28"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="24314.28"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="24314.28"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="24314.28"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="24314.28"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="24314.28"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="148-2026"/>
+    <d v="1900-01-14T00:00:00"/>
+    <d v="2026-02-02T00:00:00"/>
+    <n v="135"/>
+    <x v="4"/>
+    <s v="Filete"/>
+    <s v="2-4 (B)"/>
+    <s v="España "/>
+    <s v="Vigo"/>
+    <x v="5"/>
+    <s v="Jorge"/>
+    <n v="1650"/>
+    <n v="222750"/>
+    <n v="1480.962962962963"/>
+    <n v="22820"/>
+    <n v="199930"/>
+    <n v="5"/>
+    <s v="ODYSSEUS 606N"/>
+    <n v="59582082"/>
+    <s v="HAPAG"/>
+    <s v="PAITA"/>
+    <n v="10005721"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10005721Compensación"/>
+    <n v="1861.4473333333335"/>
+    <n v="152495.08195455416"/>
+    <n v="50378.668938514202"/>
+    <n v="2680.0173531310843"/>
+    <n v="45741.621753800559"/>
+    <n v="251295.39"/>
+    <n v="135"/>
+    <n v="1861.4473333333335"/>
+    <n v="251295.39"/>
+    <n v="-28545.390000000014"/>
+    <n v="-0.12814989898989906"/>
+    <n v="22820"/>
+    <n v="7788.461538461539"/>
+    <n v="30608.461538461539"/>
+    <n v="5418.0077097228168"/>
+    <n v="5997.9"/>
+    <n v="-58573.959248184365"/>
+    <n v="-0.26295829067647303"/>
+    <n v="12266.554488160069"/>
+    <n v="-70840.513736344437"/>
+    <n v="-0.31802699769402665"/>
+    <n v="10256.328244508353"/>
+    <n v="-48317.631003676011"/>
+    <n v="-0.21691416836667121"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="149-2026"/>
+    <d v="1900-01-15T00:00:00"/>
+    <d v="2026-02-02T00:00:00"/>
+    <n v="26.3"/>
+    <x v="0"/>
+    <s v="Rejos"/>
+    <m/>
+    <s v="España "/>
+    <s v="Vigo"/>
+    <x v="3"/>
+    <s v="Jorge"/>
+    <n v="2950"/>
+    <n v="77585"/>
+    <n v="2784.0684410646386"/>
+    <n v="4364"/>
+    <n v="73221"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="10007567"/>
+    <s v="Entradas"/>
+    <s v="FEBRERO10007567Entradas"/>
+    <n v="1829.8234619119073"/>
+    <n v="29707.86487465055"/>
+    <n v="8512.0173476594737"/>
+    <n v="540.08709224834524"/>
+    <n v="9364.3877337247959"/>
+    <n v="48124.357048283164"/>
+    <n v="26.302"/>
+    <n v="1829.8234619119073"/>
+    <n v="48129"/>
+    <n v="29460.642951716836"/>
+    <n v="0.37972086036884495"/>
+    <n v="4364"/>
+    <n v="1517.3076923076924"/>
+    <n v="5881.3076923076924"/>
+    <n v="1055.5081686348897"/>
+    <n v="2196.63"/>
+    <n v="24720.457090774256"/>
+    <n v="0.31862418110168533"/>
+    <n v="2389.7065410267396"/>
+    <n v="22330.750549747518"/>
+    <n v="0.28782303988847741"/>
+    <n v="1998.0846876338496"/>
+    <n v="26718.541778408107"/>
+    <n v="0.344377673241066"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="150-2026A"/>
+    <d v="1900-11-20T00:00:00"/>
+    <d v="2026-02-16T00:00:00"/>
+    <n v="26"/>
+    <x v="2"/>
+    <s v="Rejos"/>
+    <s v="1-2 KG"/>
+    <s v="España "/>
+    <s v="Vigo"/>
+    <x v="6"/>
+    <s v="Avelino"/>
+    <n v="2600"/>
+    <n v="67600"/>
+    <n v="2432.1538461538462"/>
+    <n v="4364"/>
+    <n v="63236"/>
+    <n v="1"/>
+    <s v="CAPE SPENCER 608N "/>
+    <n v="11400418"/>
+    <s v="HAPAG"/>
+    <s v="PAITA"/>
+    <n v="10007162"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10007162Compensación"/>
+    <n v="1715.2908173076921"/>
+    <n v="27996.817500000001"/>
+    <n v="7988.6674999999996"/>
+    <n v="415.92750000000001"/>
+    <n v="8196.1487499999894"/>
+    <n v="44597.561249999999"/>
+    <n v="26"/>
+    <n v="1715.2908173076921"/>
+    <n v="44597.561249999999"/>
+    <n v="23002.438750000001"/>
+    <n v="0.34027276257396449"/>
+    <n v="4364"/>
+    <n v="1500"/>
+    <n v="5864"/>
+    <n v="1043.4681515021723"/>
+    <n v="1897.08"/>
+    <n v="17992.05059849783"/>
+    <n v="0.26615459465233476"/>
+    <n v="2362.4475310530506"/>
+    <n v="15629.603067444779"/>
+    <n v="0.23120714596811803"/>
+    <n v="1975.2928470904976"/>
+    <n v="19967.343445588329"/>
+    <n v="0.29537490304124747"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="151-2025"/>
+    <d v="1900-01-25T00:00:00"/>
+    <d v="2026-02-27T00:00:00"/>
+    <n v="26.63"/>
+    <x v="7"/>
+    <s v="Membrana"/>
+    <m/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="7"/>
+    <m/>
+    <n v="1449.7277506571536"/>
+    <n v="38606.25"/>
+    <n v="1340.828013518588"/>
+    <n v="2900"/>
+    <n v="35706.25"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26009S"/>
+    <n v="6445502950"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10009332"/>
+    <s v="Entradas"/>
+    <s v="FEBRERO10009332Entradas"/>
+    <n v="1529.9064788732392"/>
+    <n v="33786.901123666205"/>
+    <n v="6182.6829101035864"/>
+    <n v="624.5106375055326"/>
+    <n v="147.31486111903166"/>
+    <n v="40741.409532394355"/>
+    <n v="26.625"/>
+    <n v="1529.9064788732392"/>
+    <n v="40733.759999999995"/>
+    <n v="-2135.1595323943548"/>
+    <n v="-5.5306058796033147E-2"/>
+    <n v="2900"/>
+    <n v="1536.3461538461538"/>
+    <n v="4436.3461538461543"/>
+    <n v="1068.7521874808785"/>
+    <n v="1071.1875"/>
+    <n v="-6569.070373721388"/>
+    <n v="-0.17015561919951791"/>
+    <n v="2419.6914519977972"/>
+    <n v="-8988.7618257191862"/>
+    <n v="-0.23283177790433379"/>
+    <n v="2023.1557122315364"/>
+    <n v="-4545.9146614898518"/>
+    <n v="-0.11775074402434454"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="151-2025"/>
+    <d v="1900-01-25T00:00:00"/>
+    <d v="2026-02-27T00:00:00"/>
+    <n v="26.63"/>
+    <x v="8"/>
+    <s v="Telilla"/>
+    <m/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="7"/>
+    <m/>
+    <n v="1449.7277506571536"/>
+    <n v="38606.25"/>
+    <n v="1340.828013518588"/>
+    <n v="2900"/>
+    <n v="35706.25"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26009S"/>
+    <n v="6445502950"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10009332"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10009332Compensación"/>
+    <n v="1515.6443192488266"/>
+    <n v="32833.114246992671"/>
+    <n v="5732.9992258265593"/>
+    <n v="573.74977474785271"/>
+    <n v="1221.7449740291734"/>
+    <n v="40361.608221596252"/>
+    <n v="26.625"/>
+    <n v="1515.6443192488266"/>
+    <n v="40354.030000000006"/>
+    <n v="-1755.3582215962524"/>
+    <n v="-4.5468239510344892E-2"/>
+    <n v="2900"/>
+    <n v="1536.3461538461538"/>
+    <n v="4436.3461538461543"/>
+    <n v="1068.7521874808785"/>
+    <n v="1071.1875"/>
+    <n v="-6189.2690629232857"/>
+    <n v="-0.16031779991382963"/>
+    <n v="2419.6914519977972"/>
+    <n v="-8608.9605149210838"/>
+    <n v="-0.22299395861864552"/>
+    <n v="2023.1557122315364"/>
+    <n v="-4166.1133506917495"/>
+    <n v="-0.1079129247386563"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="152-2026"/>
+    <d v="1900-01-25T00:00:00"/>
+    <d v="2026-02-09T00:00:00"/>
+    <n v="26.8"/>
+    <x v="2"/>
+    <s v="Rejos"/>
+    <s v="2-UP KG"/>
+    <s v="España "/>
+    <s v="Vigo"/>
+    <x v="6"/>
+    <s v="Avelino"/>
+    <n v="2802.0522388059699"/>
+    <n v="75095"/>
+    <n v="2639.2164179104475"/>
+    <n v="4364"/>
+    <n v="70731"/>
+    <n v="1"/>
+    <s v="GEMLIK EXPRESS 607N "/>
+    <n v="24312444"/>
+    <s v="HAPAG"/>
+    <s v="PAITA"/>
+    <n v="10007162"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10007162Compensación"/>
+    <n v="1751.18680089485"/>
+    <n v="29462.176363243641"/>
+    <n v="8406.7959078674794"/>
+    <n v="437.69722609803841"/>
+    <n v="8625.1367667728155"/>
+    <n v="46931.806263981984"/>
+    <n v="26.8"/>
+    <n v="1751.18680089485"/>
+    <n v="46931.806263981984"/>
+    <n v="28163.193736018016"/>
+    <n v="0.37503420648535879"/>
+    <n v="4364"/>
+    <n v="1546.1538461538462"/>
+    <n v="5910.1538461538457"/>
+    <n v="1075.5748638560851"/>
+    <n v="2121.9299999999998"/>
+    <n v="23299.395026008089"/>
+    <n v="0.31026559725691577"/>
+    <n v="2435.1382243162211"/>
+    <n v="20864.256801691867"/>
+    <n v="0.27783816235024789"/>
+    <n v="2036.071088539436"/>
+    <n v="25335.466114547526"/>
+    <n v="0.33737886829412778"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="156-2026A"/>
+    <d v="1900-01-26T00:00:00"/>
+    <d v="2026-02-09T00:00:00"/>
+    <n v="54"/>
+    <x v="4"/>
+    <s v="Filete"/>
+    <s v="2-4 kg 100%  blanco, No polyphosphate,no medicine"/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="8"/>
+    <m/>
+    <n v="1650"/>
+    <n v="89100"/>
+    <n v="1534.962962962963"/>
+    <n v="6212"/>
+    <n v="82888"/>
+    <n v="2"/>
+    <s v="CMA CGM IMAGINATION / 0DVITN1MA"/>
+    <s v="LMM0571149"/>
+    <s v="CMA CGM"/>
+    <s v="PAITA"/>
+    <n v="10005721"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10005721Compensación"/>
+    <n v="1740.7827151654001"/>
+    <n v="57043.95672347123"/>
+    <n v="18845.188801374748"/>
+    <n v="1002.5162251181431"/>
+    <n v="17110.604868967483"/>
+    <n v="94002.266618931608"/>
+    <n v="54"/>
+    <n v="1740.7827151654001"/>
+    <n v="94002.266618931608"/>
+    <n v="-4902.2666189316078"/>
+    <n v="-5.5019827372969787E-2"/>
+    <n v="6212"/>
+    <n v="3115.3846153846152"/>
+    <n v="9327.3846153846152"/>
+    <n v="2167.2030838891269"/>
+    <n v="2486.64"/>
+    <n v="-13910.214318205351"/>
+    <n v="-0.15611912815045287"/>
+    <n v="4906.6217952640282"/>
+    <n v="-18816.836113469381"/>
+    <n v="-0.21118783516800652"/>
+    <n v="4102.5312978033417"/>
+    <n v="-9807.6830204020098"/>
+    <n v="-0.11007500584065107"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="156-2026B"/>
+    <d v="1900-01-26T00:00:00"/>
+    <d v="2026-02-18T00:00:00"/>
+    <n v="81"/>
+    <x v="4"/>
+    <s v="Filete"/>
+    <s v="2-4 kg 100%  blanco, No polyphosphate,no medicine"/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="8"/>
+    <m/>
+    <n v="1650"/>
+    <n v="133650"/>
+    <n v="1534.962962962963"/>
+    <n v="9318"/>
+    <n v="124332"/>
+    <n v="3"/>
+    <s v="CMA CGM EXCELLENCE 0DVNNN1MA"/>
+    <s v="LMM0571699"/>
+    <s v="CMA CGM"/>
+    <s v="PAITA"/>
+    <n v="10005721"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10005721Compensación"/>
+    <n v="1740.7827151654001"/>
+    <n v="85565.935085206846"/>
+    <n v="28267.783202062124"/>
+    <n v="1503.7743376772146"/>
+    <n v="25665.907303451222"/>
+    <n v="141003.39992839741"/>
+    <n v="81"/>
+    <n v="1740.7827151654001"/>
+    <n v="141003.39992839741"/>
+    <n v="-7353.3999283974117"/>
+    <n v="-5.5019827372969787E-2"/>
+    <n v="9318"/>
+    <n v="4673.0769230769229"/>
+    <n v="13991.076923076922"/>
+    <n v="3250.8046258336904"/>
+    <n v="3729.96"/>
+    <n v="-20865.321477308025"/>
+    <n v="-0.15611912815045287"/>
+    <n v="7359.9326928960418"/>
+    <n v="-28225.254170204069"/>
+    <n v="-0.21118783516800649"/>
+    <n v="6153.7969467050116"/>
+    <n v="-14711.524530603014"/>
+    <n v="-0.11007500584065105"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="157-2026"/>
+    <d v="1900-01-27T00:00:00"/>
+    <d v="2026-02-13T00:00:00"/>
+    <n v="23.14"/>
+    <x v="3"/>
+    <s v="Conos"/>
+    <m/>
+    <s v="Tailandia"/>
+    <s v="Lat Krabang"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="2000"/>
+    <n v="48000"/>
+    <n v="1854.1666666666667"/>
+    <n v="3500"/>
+    <n v="44500"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26007S"/>
+    <n v="6445030580"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10007969"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10007969Compensación"/>
+    <n v="1397.2773083886541"/>
+    <n v="26152.438376584189"/>
+    <n v="4922.9547012673511"/>
+    <n v="386.0483765841883"/>
+    <n v="871.55546167773434"/>
+    <n v="32332.996916113458"/>
+    <n v="23.14"/>
+    <n v="1397.2773083886541"/>
+    <n v="32332.996916113458"/>
+    <n v="15667.003083886542"/>
+    <n v="0.32639589758096965"/>
+    <n v="3500"/>
+    <n v="1335"/>
+    <n v="4835"/>
+    <n v="928.68665483693326"/>
+    <n v="1335"/>
+    <n v="11238.31642904961"/>
+    <n v="0.23413159227186686"/>
+    <n v="2102.5783026372151"/>
+    <n v="9135.7381264123942"/>
+    <n v="0.19032787763359155"/>
+    <n v="1758.010633910543"/>
+    <n v="12996.327062960152"/>
+    <n v="0.27075681381166983"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="160-2026"/>
+    <d v="1900-01-29T00:00:00"/>
+    <d v="2026-02-13T00:00:00"/>
+    <n v="108"/>
+    <x v="5"/>
+    <s v="Alas"/>
+    <m/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1600"/>
+    <n v="172800"/>
+    <n v="1492.5925925925926"/>
+    <n v="11600"/>
+    <n v="161200"/>
+    <n v="4"/>
+    <s v="ECO SIROCCO 26007S"/>
+    <n v="6445031110"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10006720"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10006720Compensación"/>
+    <n v="1639.7681689527499"/>
+    <n v="114801.79673416038"/>
+    <n v="26268.81436969294"/>
+    <n v="1720.5907250163245"/>
+    <n v="34303.760418027356"/>
+    <n v="177094.96224689699"/>
+    <n v="108"/>
+    <n v="1639.7681689527499"/>
+    <n v="177094.96224689699"/>
+    <n v="-4294.9622468969901"/>
+    <n v="-2.4855105595468694E-2"/>
+    <n v="11600"/>
+    <n v="6230.7692307692305"/>
+    <n v="17830.76923076923"/>
+    <n v="4334.4061677782538"/>
+    <n v="4836"/>
+    <n v="-21624.137645444476"/>
+    <n v="-0.12513968544817405"/>
+    <n v="9813.2435905280563"/>
+    <n v="-31437.381235972534"/>
+    <n v="-0.18192928956002624"/>
+    <n v="8205.0625956066833"/>
+    <n v="-13419.075049837793"/>
+    <n v="-7.7656684316190924E-2"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="160-2026"/>
+    <d v="1900-01-29T00:00:00"/>
+    <d v="2026-02-13T00:00:00"/>
+    <n v="108"/>
+    <x v="5"/>
+    <s v="Alas"/>
+    <m/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1600"/>
+    <n v="172800"/>
+    <n v="1492.5925925925926"/>
+    <n v="11600"/>
+    <n v="161200"/>
+    <n v="4"/>
+    <s v="ECO SIROCCO 26007S"/>
+    <n v="6445031130"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10006720"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10006720Compensación"/>
+    <n v="1639.7681689527499"/>
+    <n v="114801.79673416038"/>
+    <n v="26268.81436969294"/>
+    <n v="1720.5907250163245"/>
+    <n v="34303.760418027356"/>
+    <n v="177094.96224689699"/>
+    <n v="108"/>
+    <n v="1639.7681689527499"/>
+    <n v="177094.96224689699"/>
+    <n v="-4294.9622468969901"/>
+    <n v="-2.4855105595468694E-2"/>
+    <n v="11600"/>
+    <n v="6230.7692307692305"/>
+    <n v="17830.76923076923"/>
+    <n v="4334.4061677782538"/>
+    <n v="4836"/>
+    <n v="-21624.137645444476"/>
+    <n v="-0.12513968544817405"/>
+    <n v="9813.2435905280563"/>
+    <n v="-31437.381235972534"/>
+    <n v="-0.18192928956002624"/>
+    <n v="8205.0625956066833"/>
+    <n v="-13419.075049837793"/>
+    <n v="-7.7656684316190924E-2"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="162-2026A"/>
+    <d v="1900-02-02T00:00:00"/>
+    <d v="2026-02-17T00:00:00"/>
+    <n v="115.5"/>
+    <x v="5"/>
+    <s v="Alas"/>
+    <s v="1-2 KG"/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="9"/>
+    <s v="James"/>
+    <n v="1500"/>
+    <n v="173250"/>
+    <n v="1382.987012987013"/>
+    <n v="13515"/>
+    <n v="159735"/>
+    <n v="5"/>
+    <s v="ECO SIROCCO 26007N"/>
+    <s v="LIMG02628500"/>
+    <s v="ONE"/>
+    <s v="PAITA"/>
+    <n v="10006720"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10006720Compensación"/>
+    <n v="1639.7681689527499"/>
+    <n v="122774.14372958818"/>
+    <n v="28093.037589810505"/>
+    <n v="1840.0761920313471"/>
+    <n v="36685.966002612593"/>
+    <n v="189393.22351404262"/>
+    <n v="115.5"/>
+    <n v="1639.7681689527499"/>
+    <n v="189393.22351404262"/>
+    <n v="-16143.22351404262"/>
+    <n v="-9.3178779301833312E-2"/>
+    <n v="13515"/>
+    <n v="6663.461538461539"/>
+    <n v="20178.461538461539"/>
+    <n v="4635.406596096188"/>
+    <n v="4792.05"/>
+    <n v="-36165.041648600345"/>
+    <n v="-0.20874482914055034"/>
+    <n v="10494.718839870282"/>
+    <n v="-46659.760488470623"/>
+    <n v="-0.26932040685985931"/>
+    <n v="8774.8586091904799"/>
+    <n v="-27390.183039409865"/>
+    <n v="-0.15809629459976834"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="162-2026B"/>
+    <d v="1900-02-02T00:00:00"/>
+    <d v="2026-02-17T00:00:00"/>
+    <n v="46.8"/>
+    <x v="5"/>
+    <s v="Alas"/>
+    <s v="1-2 KG"/>
+    <s v="China "/>
+    <s v="Dalian"/>
+    <x v="9"/>
+    <s v="James"/>
+    <n v="1500"/>
+    <n v="70200"/>
+    <n v="1380.2136752136753"/>
+    <n v="5606"/>
+    <n v="64594"/>
+    <n v="2"/>
+    <s v="ECO SIROCCO 26007N"/>
+    <s v="LIMG02851300"/>
+    <s v="ONE"/>
+    <s v="PAITA"/>
+    <n v="10006720"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10006720Compensación"/>
+    <n v="1639.7681689527499"/>
+    <n v="49747.4452514695"/>
+    <n v="11383.152893533606"/>
+    <n v="745.5893141737406"/>
+    <n v="14864.962847811854"/>
+    <n v="76741.150306988697"/>
+    <n v="46.8"/>
+    <n v="1639.7681689527499"/>
+    <n v="76741.150306988697"/>
+    <n v="-6541.1503069886967"/>
+    <n v="-9.3178779301833284E-2"/>
+    <n v="5606"/>
+    <n v="2700"/>
+    <n v="8306"/>
+    <n v="1878.2426727039099"/>
+    <n v="1937.82"/>
+    <n v="-14787.572979692606"/>
+    <n v="-0.21064918774490893"/>
+    <n v="4252.4055558954906"/>
+    <n v="-19039.978535588096"/>
+    <n v="-0.27122476546421787"/>
+    <n v="3555.5271247628957"/>
+    <n v="-11232.045854929711"/>
+    <n v="-0.16000065320412693"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="162-2026C"/>
+    <d v="1900-02-02T00:00:00"/>
+    <d v="2026-02-17T00:00:00"/>
+    <n v="81"/>
+    <x v="5"/>
+    <s v="Alas"/>
+    <s v="1-2 KG"/>
+    <s v="China "/>
+    <s v="Xiamen "/>
+    <x v="9"/>
+    <s v="James"/>
+    <n v="1500"/>
+    <n v="121500"/>
+    <n v="1385.0740740740741"/>
+    <n v="9309"/>
+    <n v="112191"/>
+    <n v="3"/>
+    <s v="ECO SIROCCO 26007N"/>
+    <s v="LIMG02630500"/>
+    <s v="ONE"/>
+    <s v="PAITA"/>
+    <n v="10006720"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10006720Compensación"/>
+    <n v="1639.7681689527499"/>
+    <n v="86101.347550620267"/>
+    <n v="19701.610777269703"/>
+    <n v="1290.4430437622432"/>
+    <n v="25727.820313520515"/>
+    <n v="132821.22168517273"/>
+    <n v="81"/>
+    <n v="1639.7681689527499"/>
+    <n v="132821.22168517273"/>
+    <n v="-11321.221685172728"/>
+    <n v="-9.3178779301833159E-2"/>
+    <n v="9309"/>
+    <n v="4673.0769230769229"/>
+    <n v="13982.076923076922"/>
+    <n v="3250.8046258336904"/>
+    <n v="3365.73"/>
+    <n v="-25188.373234083341"/>
+    <n v="-0.20731171386076824"/>
+    <n v="7359.9326928960418"/>
+    <n v="-32548.305926979381"/>
+    <n v="-0.26788729158007724"/>
+    <n v="6153.7969467050116"/>
+    <n v="-19034.576287378331"/>
+    <n v="-0.15666317931998627"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="164-2026"/>
+    <d v="1900-02-08T00:00:00"/>
+    <d v="2026-02-27T00:00:00"/>
+    <n v="27"/>
+    <x v="9"/>
+    <s v="Daruma"/>
+    <m/>
+    <s v="China "/>
+    <s v="Yantai"/>
+    <x v="10"/>
+    <s v="julia"/>
+    <n v="3400"/>
+    <n v="91800"/>
+    <n v="3292.5925925925926"/>
+    <n v="2900"/>
+    <n v="88900"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26009S"/>
+    <n v="6445569300"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10009239"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10009239Compensación"/>
+    <n v="2114.7381481481502"/>
+    <n v="29045.690000000031"/>
+    <n v="18974.700000000023"/>
+    <n v="365.21000000000038"/>
+    <n v="8712.3300000000127"/>
+    <n v="57097.930000000058"/>
+    <n v="27"/>
+    <n v="2114.7381481481502"/>
+    <n v="57097.930000000058"/>
+    <n v="34702.069999999942"/>
+    <n v="0.37801819172113227"/>
+    <n v="2900"/>
+    <n v="1557.6923076923076"/>
+    <n v="4457.6923076923076"/>
+    <n v="1083.6015419445635"/>
+    <n v="2667"/>
+    <n v="31827.776150363068"/>
+    <n v="0.34670780120221206"/>
+    <n v="2453.3108976320141"/>
+    <n v="29374.465252731054"/>
+    <n v="0.31998328162016398"/>
+    <n v="2051.2656489016708"/>
+    <n v="33879.041799264742"/>
+    <n v="0.36905274291138063"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="168-2026A"/>
+    <d v="1900-02-11T00:00:00"/>
+    <d v="2026-02-24T00:00:00"/>
+    <n v="351"/>
+    <x v="4"/>
+    <s v="Filete "/>
+    <s v="2-4 AA"/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="9"/>
+    <s v="James"/>
+    <n v="1300"/>
+    <n v="456300"/>
+    <n v="1300"/>
+    <n v="40339"/>
+    <n v="456300"/>
+    <n v="13"/>
+    <s v="ECO MARIN 26008N"/>
+    <n v="6445505270"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10005721"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10005721Compensación"/>
+    <n v="1740.7827151654001"/>
+    <n v="370785.71870256303"/>
+    <n v="122493.72720893587"/>
+    <n v="6516.3554632679306"/>
+    <n v="111218.93164828864"/>
+    <n v="611014.73302305548"/>
+    <n v="351"/>
+    <n v="1740.7827151654001"/>
+    <n v="611014.73302305548"/>
+    <n v="-154714.73302305548"/>
+    <n v="-0.33906362705030785"/>
+    <n v="40339"/>
+    <n v="20250"/>
+    <n v="60589"/>
+    <n v="14086.820045279324"/>
+    <n v="13689"/>
+    <n v="-215701.55306833482"/>
+    <n v="-0.47271872248155777"/>
+    <n v="31893.041669216182"/>
+    <n v="-247594.594737551"/>
+    <n v="-0.54261361984999124"/>
+    <n v="26666.453435721716"/>
+    <n v="-189035.0996326131"/>
+    <n v="-0.41427810570373241"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="168-2026B"/>
+    <d v="1900-02-11T00:00:00"/>
+    <d v="2026-02-22T00:00:00"/>
+    <n v="135"/>
+    <x v="4"/>
+    <s v="Filete "/>
+    <s v="2-4 AA"/>
+    <s v="China "/>
+    <s v="shidao"/>
+    <x v="9"/>
+    <s v="James"/>
+    <n v="1300"/>
+    <n v="175500"/>
+    <n v="1300"/>
+    <n v="15515"/>
+    <n v="175500"/>
+    <n v="5"/>
+    <s v="ECO MARIN 26008S"/>
+    <n v="6445260920"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10005721"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10005721Compensación"/>
+    <n v="1763.7777777777778"/>
+    <n v="144493.71301319491"/>
+    <n v="47735.316039620215"/>
+    <n v="2539.3976863405351"/>
+    <n v="43341.573260844343"/>
+    <n v="238110"/>
+    <n v="135"/>
+    <n v="1763.7777777777778"/>
+    <n v="238110"/>
+    <n v="-62610"/>
+    <n v="-0.35675213675213674"/>
+    <n v="15515"/>
+    <n v="7788.461538461539"/>
+    <n v="23303.461538461539"/>
+    <n v="5418.0077097228168"/>
+    <n v="5265"/>
+    <n v="-86066.469248184352"/>
+    <n v="-0.49040723218338661"/>
+    <n v="12266.554488160069"/>
+    <n v="-98333.023736344418"/>
+    <n v="-0.56030212955182002"/>
+    <n v="10256.328244508353"/>
+    <n v="-75810.141003675992"/>
+    <n v="-0.43196661540556119"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="168-2026C"/>
+    <d v="1900-02-11T00:00:00"/>
+    <d v="2026-02-22T00:00:00"/>
+    <n v="54"/>
+    <x v="4"/>
+    <s v="Filete "/>
+    <s v="2-4 AA"/>
+    <s v="China "/>
+    <s v="Xiamen "/>
+    <x v="9"/>
+    <s v="James"/>
+    <n v="1300"/>
+    <n v="70200"/>
+    <n v="1300"/>
+    <n v="6206"/>
+    <n v="70200"/>
+    <n v="2"/>
+    <s v="ECO MARIN 26008S"/>
+    <n v="6445502930"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10005721"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10005721Compensación"/>
+    <n v="1740.7827151654001"/>
+    <n v="57043.95672347123"/>
+    <n v="18845.188801374748"/>
+    <n v="1002.5162251181431"/>
+    <n v="17110.604868967483"/>
+    <n v="94002.266618931608"/>
+    <n v="54"/>
+    <n v="1740.7827151654001"/>
+    <n v="94002.266618931608"/>
+    <n v="-23802.266618931608"/>
+    <n v="-0.33906362705030779"/>
+    <n v="6206"/>
+    <n v="3115.3846153846152"/>
+    <n v="9321.3846153846152"/>
+    <n v="2167.2030838891269"/>
+    <n v="2106"/>
+    <n v="-33184.854318205355"/>
+    <n v="-0.47271872248155777"/>
+    <n v="4906.6217952640282"/>
+    <n v="-38091.476113469384"/>
+    <n v="-0.54261361984999124"/>
+    <n v="4102.5312978033417"/>
+    <n v="-29082.323020402015"/>
+    <n v="-0.41427810570373241"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <s v="170-2026A"/>
+    <d v="1900-02-11T00:00:00"/>
+    <d v="2026-02-23T00:00:00"/>
+    <n v="156"/>
+    <x v="2"/>
+    <s v="Rejos"/>
+    <s v="9 FCL 1-2 / 1 FCL 2-UP"/>
+    <s v="España "/>
+    <s v="Vigo"/>
+    <x v="11"/>
+    <s v="Ramon"/>
+    <n v="2500"/>
+    <n v="390000"/>
+    <n v="2337.2307692307691"/>
+    <n v="25392"/>
+    <n v="364608"/>
+    <n v="4"/>
+    <s v="CAPE SABLE 609N"/>
+    <n v="11428031"/>
+    <s v="HAPAG"/>
+    <s v="PAITA"/>
+    <n v="10007162"/>
+    <s v="Compensación"/>
+    <s v="FEBRERO10007162Compensación"/>
+    <n v="1715.2908173076921"/>
+    <n v="167980.905"/>
+    <n v="47932.004999999997"/>
+    <n v="2495.5650000000001"/>
+    <n v="49176.892499999936"/>
+    <n v="267585.36749999999"/>
+    <n v="156"/>
+    <n v="1715.2908173076921"/>
+    <n v="267585.36749999999"/>
+    <n v="122414.63250000001"/>
+    <n v="0.31388367307692311"/>
+    <n v="25392"/>
+    <n v="9000"/>
+    <n v="34392"/>
+    <n v="6260.8089090130334"/>
+    <n v="10938.24"/>
+    <n v="92700.063590986974"/>
+    <n v="0.23769247074612046"/>
+    <n v="14174.685186318302"/>
+    <n v="78525.378404668678"/>
+    <n v="0.20134712411453506"/>
+    <n v="11851.757082542987"/>
+    <n v="104551.82067352996"/>
+    <n v="0.26808159147058963"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="FEBRERO"/>
+    <m/>
+    <d v="2026-02-27T00:00:00"/>
+    <d v="2026-02-27T00:00:00"/>
+    <n v="0"/>
+    <x v="6"/>
+    <s v="Residuos"/>
+    <s v="Residuos"/>
+    <s v="Residuos"/>
+    <s v="Residuos"/>
+    <x v="4"/>
+    <m/>
+    <n v="0"/>
+    <n v="40026"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="40026"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="40026"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="40026"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="40026"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="40026"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="150-2026B"/>
+    <d v="1900-11-20T00:00:00"/>
+    <d v="2026-03-03T00:00:00"/>
+    <n v="52"/>
+    <x v="2"/>
+    <s v="Rejos"/>
+    <s v="1-2 KG"/>
+    <s v="España "/>
+    <s v="Vigo"/>
+    <x v="6"/>
+    <s v="Avelino"/>
+    <n v="2600"/>
+    <n v="135200"/>
+    <n v="2518.6153846153848"/>
+    <n v="4232"/>
+    <n v="130968"/>
+    <n v="1"/>
+    <s v="LEONIDAS Z 610N"/>
+    <n v="51077247"/>
+    <m/>
+    <m/>
+    <n v="10007162"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10007162Inventario final"/>
+    <n v="1720"/>
+    <n v="56147.360192931876"/>
+    <n v="16021.200390087792"/>
+    <n v="834.14012250190274"/>
+    <n v="16437.299294478424"/>
+    <n v="89440"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="45760"/>
+    <n v="0.33846153846153848"/>
+    <n v="4232"/>
+    <n v="3000"/>
+    <n v="7232"/>
+    <n v="1839.0870557613375"/>
+    <n v="3929.04"/>
+    <n v="40617.952944238663"/>
+    <n v="0.30042864603726821"/>
+    <n v="2750.8223846230853"/>
+    <n v="37867.13055961558"/>
+    <n v="0.2800823266243756"/>
+    <n v="3214.1286415056566"/>
+    <n v="43832.081585744323"/>
+    <n v="0.32420178687680712"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="150-2026C"/>
+    <d v="1900-11-20T00:00:00"/>
+    <d v="2026-03-03T00:00:00"/>
+    <n v="52"/>
+    <x v="2"/>
+    <s v="Rejos"/>
+    <s v="1-2 KG"/>
+    <s v="España "/>
+    <s v="Vigo"/>
+    <x v="6"/>
+    <s v="Avelino"/>
+    <n v="2600"/>
+    <n v="135200"/>
+    <n v="2518.6153846153848"/>
+    <n v="4232"/>
+    <n v="130968"/>
+    <n v="1"/>
+    <s v="LEONIDAS Z 610N"/>
+    <n v="37563181"/>
+    <m/>
+    <m/>
+    <n v="10007162"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10007162Inventario final"/>
+    <n v="1720"/>
+    <n v="56147.360192931876"/>
+    <n v="16021.200390087792"/>
+    <n v="834.14012250190274"/>
+    <n v="16437.299294478424"/>
+    <n v="89440"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="45760"/>
+    <n v="0.33846153846153848"/>
+    <n v="4232"/>
+    <n v="3000"/>
+    <n v="7232"/>
+    <n v="1839.0870557613375"/>
+    <n v="3929.04"/>
+    <n v="40617.952944238663"/>
+    <n v="0.30042864603726821"/>
+    <n v="2750.8223846230853"/>
+    <n v="37867.13055961558"/>
+    <n v="0.2800823266243756"/>
+    <n v="3214.1286415056566"/>
+    <n v="43832.081585744323"/>
+    <n v="0.32420178687680712"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="159-2026A"/>
+    <d v="1900-01-29T00:00:00"/>
+    <d v="2026-03-03T00:00:00"/>
+    <n v="24"/>
+    <x v="4"/>
+    <s v="Filete"/>
+    <s v="B"/>
+    <s v="Japón "/>
+    <s v="Sendai"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1700"/>
+    <n v="40800"/>
+    <n v="1562.375"/>
+    <n v="3303"/>
+    <n v="37497"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26009N"/>
+    <s v="LIMG03265300"/>
+    <s v="ONE"/>
+    <s v="PAITA"/>
+    <n v="10005721"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005721Inventario final"/>
+    <n v="1740"/>
+    <n v="25341.469852777249"/>
+    <n v="8371.8734501256513"/>
+    <n v="445.36290049708072"/>
+    <n v="7601.2937966000209"/>
+    <n v="41760"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-960"/>
+    <n v="-2.3529411764705882E-2"/>
+    <n v="3303"/>
+    <n v="1384.6153846153848"/>
+    <n v="4687.6153846153848"/>
+    <n v="848.80941035138653"/>
+    <n v="1124.9099999999999"/>
+    <n v="-5371.5147949667717"/>
+    <n v="-0.13165477438644049"/>
+    <n v="1269.6103313645008"/>
+    <n v="-6641.1251263312724"/>
+    <n v="-0.16277267466498216"/>
+    <n v="1483.443988387226"/>
+    <n v="-3888.0708065795457"/>
+    <n v="-9.5295853102439848E-2"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="161-2026A"/>
+    <d v="1900-01-29T00:00:00"/>
+    <d v="2026-03-04T00:00:00"/>
+    <n v="72"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="500-up"/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1400"/>
+    <n v="100800"/>
+    <n v="1266.5416666666667"/>
+    <n v="9609"/>
+    <n v="91191"/>
+    <n v="3"/>
+    <s v="ECO SIROCCO 26009N"/>
+    <s v="LIMG03094300"/>
+    <s v="ONE LINE"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="81515.847234083616"/>
+    <n v="29485.475655513077"/>
+    <n v="976.89119234288887"/>
+    <n v="21941.78591806041"/>
+    <n v="133920"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-33120"/>
+    <n v="-0.32857142857142857"/>
+    <n v="9609"/>
+    <n v="4153.8461538461543"/>
+    <n v="13762.846153846154"/>
+    <n v="2546.4282310541598"/>
+    <n v="2735.73"/>
+    <n v="-46693.544384900313"/>
+    <n v="-0.46322960699305865"/>
+    <n v="3808.8309940935028"/>
+    <n v="-50502.375378993813"/>
+    <n v="-0.50101562875985928"/>
+    <n v="4450.3319651616785"/>
+    <n v="-42243.212419738637"/>
+    <n v="-0.4190794882910579"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="161-2026B"/>
+    <d v="1900-01-29T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="48"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="500-up"/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1400"/>
+    <n v="67200"/>
+    <n v="1254.1666666666667"/>
+    <n v="7000"/>
+    <n v="60200"/>
+    <n v="2"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <n v="6446527790"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="54343.898156055744"/>
+    <n v="19656.983770342053"/>
+    <n v="651.26079489525921"/>
+    <n v="14627.857278706941"/>
+    <n v="89280"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-22080"/>
+    <n v="-0.32857142857142857"/>
+    <n v="7000"/>
+    <n v="2769.2307692307695"/>
+    <n v="9769.2307692307695"/>
+    <n v="1697.6188207027731"/>
+    <n v="1806"/>
+    <n v="-31740.849589933539"/>
+    <n v="-0.47233407127877292"/>
+    <n v="2539.2206627290016"/>
+    <n v="-34280.070252662539"/>
+    <n v="-0.51012009304557349"/>
+    <n v="2966.887976774452"/>
+    <n v="-28773.961613159088"/>
+    <n v="-0.42818395257677216"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="163-2026"/>
+    <d v="1900-02-02T00:00:00"/>
+    <d v="2026-03-06T00:00:00"/>
+    <n v="48"/>
+    <x v="5"/>
+    <s v="Alas"/>
+    <s v="1-up"/>
+    <s v="korea"/>
+    <s v="Busan"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1600"/>
+    <n v="76800"/>
+    <n v="1479.1666666666667"/>
+    <n v="5800"/>
+    <n v="71000"/>
+    <n v="2"/>
+    <s v="ECO MARIN 26010S"/>
+    <n v="6445718250"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10006720"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10006720Inventario final"/>
+    <n v="1640"/>
+    <n v="51030.234029991967"/>
+    <n v="11676.679950572587"/>
+    <n v="764.81419043806204"/>
+    <n v="15248.271828997389"/>
+    <n v="78720"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-1920"/>
+    <n v="-2.5000000000000001E-2"/>
+    <n v="5800"/>
+    <n v="2769.2307692307695"/>
+    <n v="8569.2307692307695"/>
+    <n v="1697.6188207027731"/>
+    <n v="2130"/>
+    <n v="-10056.849589933543"/>
+    <n v="-0.13094856236892635"/>
+    <n v="2539.2206627290016"/>
+    <n v="-12596.070252662545"/>
+    <n v="-0.16401133141487689"/>
+    <n v="2966.887976774452"/>
+    <n v="-7089.961613159091"/>
+    <n v="-9.231720850467566E-2"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="165-2026"/>
+    <d v="1900-02-08T00:00:00"/>
+    <d v="2026-03-24T00:00:00"/>
+    <n v="27"/>
+    <x v="7"/>
+    <s v="Membrana"/>
+    <m/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="8"/>
+    <m/>
+    <n v="1400"/>
+    <n v="37800"/>
+    <n v="1271.6296296296296"/>
+    <n v="3466"/>
+    <n v="34334"/>
+    <n v="1"/>
+    <s v="CMA CGM BETTER WAYS 0DVOHN1MA"/>
+    <s v="LMM0577574"/>
+    <s v="CMA CGM"/>
+    <s v="PAITA"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="37800"/>
+    <n v="1"/>
+    <n v="3466"/>
+    <n v="1557.6923076923076"/>
+    <n v="5023.6923076923076"/>
+    <n v="954.91058664530988"/>
+    <n v="1030.02"/>
+    <n v="32851.417105662382"/>
+    <n v="0.86908510861540689"/>
+    <n v="1428.3116227850635"/>
+    <n v="31423.105482877319"/>
+    <n v="0.83129908684860632"/>
+    <n v="1668.8744869356292"/>
+    <n v="34520.291592598012"/>
+    <n v="0.91323522731740769"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="167-2026"/>
+    <d v="1900-02-10T00:00:00"/>
+    <d v="2026-03-23T00:00:00"/>
+    <n v="48"/>
+    <x v="3"/>
+    <s v="Conos"/>
+    <m/>
+    <s v="Tailandia"/>
+    <s v="Bangkok"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1600"/>
+    <n v="76800"/>
+    <n v="1462.5"/>
+    <n v="6600"/>
+    <n v="70200"/>
+    <n v="2"/>
+    <s v="ECO MARIN 26012S"/>
+    <n v="6446513180"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10007969"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10007969Inventario final"/>
+    <n v="1400"/>
+    <n v="54354.508379726183"/>
+    <n v="10231.733201803394"/>
+    <n v="802.340930980042"/>
+    <n v="1811.4174874903686"/>
+    <n v="67200"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="9600"/>
+    <n v="0.125"/>
+    <n v="6600"/>
+    <n v="2769.2307692307695"/>
+    <n v="9369.2307692307695"/>
+    <n v="1697.6188207027731"/>
+    <n v="2106"/>
+    <n v="639.15041006645743"/>
+    <n v="8.3222709644069984E-3"/>
+    <n v="2539.2206627290016"/>
+    <n v="-1900.0702526625441"/>
+    <n v="-2.4740498081543542E-2"/>
+    <n v="2966.887976774452"/>
+    <n v="3606.0383868409094"/>
+    <n v="4.6953624828657677E-2"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="169-2026A"/>
+    <d v="1900-02-11T00:00:00"/>
+    <d v="2026-03-03T00:00:00"/>
+    <n v="116.8"/>
+    <x v="5"/>
+    <s v="Alas"/>
+    <s v="1-up"/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1600"/>
+    <n v="186880"/>
+    <n v="1484.2893835616439"/>
+    <n v="13515"/>
+    <n v="173365"/>
+    <n v="5"/>
+    <s v="ECO SIROCCO 26009N"/>
+    <s v="LIMG02789600"/>
+    <s v="ONE"/>
+    <s v="PAITA"/>
+    <n v="10006720"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10006720Inventario final"/>
+    <n v="1640"/>
+    <n v="124173.56947298045"/>
+    <n v="28413.254546393295"/>
+    <n v="1861.0478633992841"/>
+    <n v="37104.128117226981"/>
+    <n v="191552"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-4672"/>
+    <n v="-2.5000000000000001E-2"/>
+    <n v="13515"/>
+    <n v="6738.4615384615381"/>
+    <n v="20253.461538461539"/>
+    <n v="4130.8724637100813"/>
+    <n v="5200.95"/>
+    <n v="-23855.384002171621"/>
+    <n v="-0.12765081336778478"/>
+    <n v="6178.7702793072376"/>
+    <n v="-30034.154281478859"/>
+    <n v="-0.16071358241373535"/>
+    <n v="7219.4274101511664"/>
+    <n v="-16635.956592020455"/>
+    <n v="-8.9019459503534112E-2"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="169-2026B"/>
+    <d v="1900-02-11T00:00:00"/>
+    <d v="2026-03-10T00:00:00"/>
+    <n v="135"/>
+    <x v="5"/>
+    <s v="Alas"/>
+    <s v="1-up"/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1600"/>
+    <n v="216000"/>
+    <n v="1519.911111111111"/>
+    <n v="10812"/>
+    <n v="205188"/>
+    <n v="4"/>
+    <s v="ECO MARIN 26010N"/>
+    <s v="LIMG03633900"/>
+    <s v="ONE"/>
+    <s v="PAITA"/>
+    <n v="10006720"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10006720Inventario final"/>
+    <n v="1640"/>
+    <n v="143522.5332093524"/>
+    <n v="32840.6623609854"/>
+    <n v="2151.0399106070495"/>
+    <n v="42885.764519055156"/>
+    <n v="221400"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-5400"/>
+    <n v="-2.5000000000000001E-2"/>
+    <n v="10812"/>
+    <n v="7788.461538461539"/>
+    <n v="18600.461538461539"/>
+    <n v="4774.5529332265496"/>
+    <n v="6155.6399999999994"/>
+    <n v="-22619.37447168809"/>
+    <n v="-0.10471932625781523"/>
+    <n v="7141.5581139253172"/>
+    <n v="-29760.932585613409"/>
+    <n v="-0.13778209530376578"/>
+    <n v="8344.3724346781455"/>
+    <n v="-14275.002037009945"/>
+    <n v="-6.6087972393564565E-2"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="170-2026B"/>
+    <d v="1900-02-11T00:00:00"/>
+    <d v="2026-03-11T00:00:00"/>
+    <n v="78"/>
+    <x v="2"/>
+    <s v="Rejos"/>
+    <s v=" 1-2 "/>
+    <s v="España "/>
+    <s v="Vigo"/>
+    <x v="11"/>
+    <s v="Ramon"/>
+    <n v="2400"/>
+    <n v="187200"/>
+    <n v="2243.0865384615386"/>
+    <n v="12239.25"/>
+    <n v="174960.75"/>
+    <n v="3"/>
+    <s v="CMA CGM BOLDNESS / 0DVODN1MA"/>
+    <s v="LMM0575562"/>
+    <s v="CMA CGM"/>
+    <m/>
+    <n v="10007162"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10007162Inventario final"/>
+    <n v="1720"/>
+    <n v="84221.040289397817"/>
+    <n v="24031.800585131685"/>
+    <n v="1251.2101837528539"/>
+    <n v="24655.948941717637"/>
+    <n v="134160"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="53040"/>
+    <n v="0.28333333333333333"/>
+    <n v="12239.25"/>
+    <n v="4500"/>
+    <n v="16739.25"/>
+    <n v="2758.6305836420065"/>
+    <n v="5248.8225000000002"/>
+    <n v="38790.941916357995"/>
+    <n v="0.20721657006601493"/>
+    <n v="4126.2335769346282"/>
+    <n v="34664.708339423363"/>
+    <n v="0.18517472403538121"/>
+    <n v="4821.1929622584848"/>
+    <n v="43612.134878616482"/>
+    <n v="0.23297080597551539"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="171-2026"/>
+    <d v="1900-02-12T00:00:00"/>
+    <d v="2026-03-04T00:00:00"/>
+    <n v="135"/>
+    <x v="4"/>
+    <s v="Filete "/>
+    <s v="2-4 AA"/>
+    <s v="China "/>
+    <s v="shidao"/>
+    <x v="12"/>
+    <m/>
+    <n v="1450"/>
+    <n v="195750"/>
+    <n v="1338.7777777777778"/>
+    <n v="15015"/>
+    <n v="180735"/>
+    <n v="5"/>
+    <s v="ECO SIROCCO 26009N"/>
+    <s v="LIMG03093900"/>
+    <s v="ONE"/>
+    <s v="PAITA"/>
+    <n v="10005721"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005721Inventario final"/>
+    <n v="1740"/>
+    <n v="142545.76792187203"/>
+    <n v="47091.788156956783"/>
+    <n v="2505.1663152960791"/>
+    <n v="42757.277605875119"/>
+    <n v="234900"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-39150"/>
+    <n v="-0.2"/>
+    <n v="15015"/>
+    <n v="7788.461538461539"/>
+    <n v="22803.461538461539"/>
+    <n v="4774.5529332265496"/>
+    <n v="5422.05"/>
+    <n v="-61305.964471688087"/>
+    <n v="-0.31318500368678459"/>
+    <n v="7141.5581139253172"/>
+    <n v="-68447.522585613406"/>
+    <n v="-0.34966805918576455"/>
+    <n v="8344.3724346781455"/>
+    <n v="-52961.592037009941"/>
+    <n v="-0.27055730287105972"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="172-2026A"/>
+    <d v="1900-02-15T00:00:00"/>
+    <d v="2026-03-11T00:00:00"/>
+    <n v="150"/>
+    <x v="2"/>
+    <s v="Rejos"/>
+    <s v="1-2 KG "/>
+    <s v="España "/>
+    <s v="Vigo"/>
+    <x v="11"/>
+    <s v="Ramon"/>
+    <n v="2300"/>
+    <n v="345000"/>
+    <n v="2139.1"/>
+    <n v="24135"/>
+    <n v="320865"/>
+    <n v="6"/>
+    <s v="CMA CGM BOLDNESS / 0DVODN1MA"/>
+    <s v="LMM0575536"/>
+    <s v="CMA CGM"/>
+    <m/>
+    <n v="10007162"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10007162Inventario final"/>
+    <n v="1720"/>
+    <n v="161963.53901807271"/>
+    <n v="46215.001125253242"/>
+    <n v="2406.1734302939499"/>
+    <n v="47415.286426380073"/>
+    <n v="258000"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="87000"/>
+    <n v="0.25217391304347825"/>
+    <n v="24135"/>
+    <n v="8653.8461538461543"/>
+    <n v="32788.846153846156"/>
+    <n v="5305.0588146961663"/>
+    <n v="9625.9499999999989"/>
+    <n v="58532.045031457674"/>
+    <n v="0.16965810154045702"/>
+    <n v="7935.0645710281306"/>
+    <n v="50596.980460429542"/>
+    <n v="0.14665791437805664"/>
+    <n v="9271.5249274201633"/>
+    <n v="67803.569958877837"/>
+    <n v="0.19653208683732706"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="172-2026A"/>
+    <d v="1900-02-15T00:00:00"/>
+    <d v="2026-03-11T00:00:00"/>
+    <n v="25"/>
+    <x v="0"/>
+    <s v="Rejos"/>
+    <m/>
+    <s v="España "/>
+    <s v="Vigo"/>
+    <x v="11"/>
+    <s v="Ramon"/>
+    <n v="2500"/>
+    <n v="62500"/>
+    <n v="2336.7199999999998"/>
+    <n v="4082"/>
+    <n v="58418"/>
+    <n v="1"/>
+    <s v="CMA CGM BOLDNESS / 0DVODN1MA"/>
+    <s v="LMM0575536"/>
+    <s v="CMA CGM"/>
+    <m/>
+    <n v="10007567"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10007567Inventario final"/>
+    <n v="1700"/>
+    <n v="26806.783508435394"/>
+    <n v="7351.4498031009725"/>
+    <n v="459.62755284063434"/>
+    <n v="7882.1391356229988"/>
+    <n v="42500"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="20000"/>
+    <n v="0.32"/>
+    <n v="4082"/>
+    <n v="1442.3076923076924"/>
+    <n v="5524.3076923076924"/>
+    <n v="884.17646911602765"/>
+    <n v="1752.54"/>
+    <n v="15344.055838576282"/>
+    <n v="0.24550489341722051"/>
+    <n v="1322.5107618380218"/>
+    <n v="14021.545076738259"/>
+    <n v="0.22434472122781215"/>
+    <n v="1545.2541545700271"/>
+    <n v="16889.309993146308"/>
+    <n v="0.2702289598903409"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="172-2026B"/>
+    <d v="1900-02-15T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="54"/>
+    <x v="10"/>
+    <s v="Alas"/>
+    <s v="0.3 - UP "/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="11"/>
+    <s v="Ramon"/>
+    <n v="3350"/>
+    <n v="180900"/>
+    <n v="3242.5925925925926"/>
+    <n v="5800"/>
+    <n v="175100"/>
+    <n v="2"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <n v="6446512380"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10009331"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10009331Inventario final"/>
+    <n v="1810"/>
+    <n v="56742.198519184363"/>
+    <n v="22722.689817285758"/>
+    <n v="1023.6040864186556"/>
+    <n v="17251.507577111213"/>
+    <n v="97740"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="83160"/>
+    <n v="0.45970149253731341"/>
+    <n v="5800"/>
+    <n v="3115.3846153846152"/>
+    <n v="8915.3846153846152"/>
+    <n v="1909.8211732906198"/>
+    <n v="5253"/>
+    <n v="77587.79421132477"/>
+    <n v="0.42889880713833484"/>
+    <n v="2856.623245570127"/>
+    <n v="74731.170965754645"/>
+    <n v="0.41310763386265698"/>
+    <n v="3337.7489738712584"/>
+    <n v="80925.543185196031"/>
+    <n v="0.44734960301379784"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="174-2026"/>
+    <d v="1900-02-17T00:00:00"/>
+    <d v="2026-03-10T00:00:00"/>
+    <n v="108"/>
+    <x v="4"/>
+    <s v="Filete "/>
+    <s v="2-4 AA"/>
+    <s v="China "/>
+    <s v="shidao"/>
+    <x v="12"/>
+    <m/>
+    <n v="1450"/>
+    <n v="156600"/>
+    <n v="1338.7777777777778"/>
+    <n v="12012"/>
+    <n v="144588"/>
+    <n v="4"/>
+    <s v="ECO MARIN 26010N"/>
+    <s v="LIMG03595900"/>
+    <m/>
+    <m/>
+    <n v="10005721"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005721Inventario final"/>
+    <n v="1740"/>
+    <n v="114036.61433749762"/>
+    <n v="37673.430525565425"/>
+    <n v="2004.1330522368633"/>
+    <n v="34205.822084700092"/>
+    <n v="187920"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-31320"/>
+    <n v="-0.2"/>
+    <n v="12012"/>
+    <n v="6230.7692307692305"/>
+    <n v="18242.76923076923"/>
+    <n v="3819.6423465812395"/>
+    <n v="4337.6399999999994"/>
+    <n v="-49044.771577350475"/>
+    <n v="-0.31318500368678465"/>
+    <n v="5713.246491140254"/>
+    <n v="-54758.018068490732"/>
+    <n v="-0.34966805918576455"/>
+    <n v="6675.4979477425168"/>
+    <n v="-42369.27362960796"/>
+    <n v="-0.27055730287105978"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="175-2026"/>
+    <d v="1900-02-17T00:00:00"/>
+    <d v="2026-03-18T00:00:00"/>
+    <n v="26"/>
+    <x v="4"/>
+    <s v="Filete "/>
+    <s v="2-4 AA"/>
+    <s v="Klaipeda"/>
+    <s v="Lituania"/>
+    <x v="13"/>
+    <m/>
+    <n v="1500"/>
+    <n v="39000"/>
+    <n v="1230.9615384615386"/>
+    <n v="6995"/>
+    <n v="32005"/>
+    <n v="1"/>
+    <s v="CMA CGM VOLTAIRE / 0DVOFN1MA"/>
+    <s v="LMM0575667"/>
+    <n v="1"/>
+    <s v="CMA CGM"/>
+    <n v="10005721"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005721Inventario final"/>
+    <n v="1740"/>
+    <n v="27453.259007175351"/>
+    <n v="9069.5295709694547"/>
+    <n v="482.47647553850408"/>
+    <n v="8234.7349463166884"/>
+    <n v="45240"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-6240"/>
+    <n v="-0.16"/>
+    <n v="6995"/>
+    <n v="1500"/>
+    <n v="8495"/>
+    <n v="919.54352788066876"/>
+    <n v="960.15"/>
+    <n v="-14694.393527880669"/>
+    <n v="-0.37677932122770946"/>
+    <n v="1375.4111923115427"/>
+    <n v="-16069.804720192213"/>
+    <n v="-0.41204627487672341"/>
+    <n v="1607.0643207528283"/>
+    <n v="-13087.329207127841"/>
+    <n v="-0.33557254377250872"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="176-2026A"/>
+    <d v="1900-02-17T00:00:00"/>
+    <d v="2026-03-23T00:00:00"/>
+    <n v="54"/>
+    <x v="5"/>
+    <s v="Alas"/>
+    <s v="1-up"/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1600"/>
+    <n v="86400"/>
+    <n v="1492.5925925925926"/>
+    <n v="5800"/>
+    <n v="80600"/>
+    <n v="2"/>
+    <s v="ECO SIROCCO 26011S"/>
+    <n v="6446527810"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10006720"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10006720Inventario final"/>
+    <n v="1640"/>
+    <n v="57409.013283740962"/>
+    <n v="13136.264944394159"/>
+    <n v="860.41596424281977"/>
+    <n v="17154.305807622062"/>
+    <n v="88560"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-2160"/>
+    <n v="-2.5000000000000001E-2"/>
+    <n v="5800"/>
+    <n v="3115.3846153846152"/>
+    <n v="8915.3846153846152"/>
+    <n v="1909.8211732906198"/>
+    <n v="2418"/>
+    <n v="-10567.205788675235"/>
+    <n v="-0.12230562255411152"/>
+    <n v="2856.623245570127"/>
+    <n v="-13423.829034245362"/>
+    <n v="-0.15536839160006205"/>
+    <n v="3337.7489738712584"/>
+    <n v="-7229.4568148039771"/>
+    <n v="-8.3674268689860845E-2"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="176-2026B"/>
+    <d v="1900-02-17T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="81"/>
+    <x v="5"/>
+    <s v="Alas"/>
+    <s v="1-up"/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1600"/>
+    <n v="129600"/>
+    <n v="1499.5185185185185"/>
+    <n v="8139"/>
+    <n v="121461"/>
+    <n v="3"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <s v="LIMG04326900"/>
+    <s v="ONE LINE"/>
+    <s v="PAITA"/>
+    <n v="10006720"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10006720Inventario final"/>
+    <n v="1640"/>
+    <n v="86113.519925611443"/>
+    <n v="19704.39741659124"/>
+    <n v="1290.6239463642296"/>
+    <n v="25731.458711433093"/>
+    <n v="132840"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-3240"/>
+    <n v="-2.5000000000000001E-2"/>
+    <n v="8139"/>
+    <n v="4673.0769230769229"/>
+    <n v="12812.076923076922"/>
+    <n v="2864.7317599359299"/>
+    <n v="3643.83"/>
+    <n v="-15272.978683012852"/>
+    <n v="-0.1178470577392967"/>
+    <n v="4284.9348683551907"/>
+    <n v="-19557.913551368045"/>
+    <n v="-0.15090982678524725"/>
+    <n v="5006.623460806888"/>
+    <n v="-10266.355222205964"/>
+    <n v="-7.921570387504602E-2"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="177-2026A"/>
+    <d v="1900-02-18T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="48"/>
+    <x v="5"/>
+    <s v="Alas"/>
+    <s v="1-up"/>
+    <s v="korea"/>
+    <s v="Busan"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1600"/>
+    <n v="76800"/>
+    <n v="1486.9583333333333"/>
+    <n v="5426"/>
+    <n v="71374"/>
+    <n v="2"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <s v="LIMG04588500"/>
+    <s v="ONE LINE"/>
+    <s v="PAITA"/>
+    <n v="10006720"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10006720Inventario final"/>
+    <n v="1640"/>
+    <n v="51030.234029991967"/>
+    <n v="11676.679950572587"/>
+    <n v="764.81419043806204"/>
+    <n v="15248.271828997389"/>
+    <n v="78720"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-1920"/>
+    <n v="-2.5000000000000001E-2"/>
+    <n v="5426"/>
+    <n v="2769.2307692307695"/>
+    <n v="8195.2307692307695"/>
+    <n v="1697.6188207027731"/>
+    <n v="2141.2199999999998"/>
+    <n v="-9671.6295899335437"/>
+    <n v="-0.12593267695225968"/>
+    <n v="2539.2206627290016"/>
+    <n v="-12210.850252662545"/>
+    <n v="-0.15899544599821022"/>
+    <n v="2966.887976774452"/>
+    <n v="-6704.7416131590917"/>
+    <n v="-8.7301323088009003E-2"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="179-2026A"/>
+    <d v="1900-02-22T00:00:00"/>
+    <d v="2026-03-20T00:00:00"/>
+    <n v="24"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="500-up"/>
+    <s v="Tailandia "/>
+    <s v="Laem chabang"/>
+    <x v="1"/>
+    <s v="ACER FOOD"/>
+    <n v="1100"/>
+    <n v="26400"/>
+    <n v="966.54166666666663"/>
+    <n v="3203"/>
+    <n v="23197"/>
+    <n v="1"/>
+    <s v="ECO MARIN 26012N"/>
+    <s v="LIMG03918800"/>
+    <s v="ONE LINE"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="27171.949078027872"/>
+    <n v="9828.4918851710263"/>
+    <n v="325.6303974476296"/>
+    <n v="7313.9286393534703"/>
+    <n v="44640"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-18240"/>
+    <n v="-0.69090909090909092"/>
+    <n v="3203"/>
+    <n v="1384.6153846153848"/>
+    <n v="4587.6153846153848"/>
+    <n v="848.80941035138653"/>
+    <n v="695.91"/>
+    <n v="-22980.51479496677"/>
+    <n v="-0.87047404526389283"/>
+    <n v="1269.6103313645008"/>
+    <n v="-24250.12512633127"/>
+    <n v="-0.91856534569436632"/>
+    <n v="1483.443988387226"/>
+    <n v="-21497.070806579544"/>
+    <n v="-0.81428298509771002"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="179-2026B1"/>
+    <d v="1900-02-22T00:00:00"/>
+    <d v="2026-03-20T00:00:00"/>
+    <n v="24"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="500-up"/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="1"/>
+    <s v="Julieta"/>
+    <n v="1100"/>
+    <n v="26400"/>
+    <n v="953.625"/>
+    <n v="3513"/>
+    <n v="22887"/>
+    <n v="1"/>
+    <s v="ECO MARIN 26012N"/>
+    <s v="LIMG03924500"/>
+    <s v="ONE LINE"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="27171.949078027872"/>
+    <n v="9828.4918851710263"/>
+    <n v="325.6303974476296"/>
+    <n v="7313.9286393534703"/>
+    <n v="44640"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-18240"/>
+    <n v="-0.69090909090909092"/>
+    <n v="3513"/>
+    <n v="1384.6153846153848"/>
+    <n v="4897.6153846153848"/>
+    <n v="848.80941035138653"/>
+    <n v="686.61"/>
+    <n v="-23299.814794966769"/>
+    <n v="-0.88256874223358972"/>
+    <n v="1269.6103313645008"/>
+    <n v="-24569.425126331269"/>
+    <n v="-0.93066004266406321"/>
+    <n v="1483.443988387226"/>
+    <n v="-21816.370806579544"/>
+    <n v="-0.82637768206740692"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="179-2026B2"/>
+    <d v="1900-02-22T00:00:00"/>
+    <d v="2026-03-20T00:00:00"/>
+    <n v="24"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="500-up"/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="1"/>
+    <s v="Julieta"/>
+    <n v="1100"/>
+    <n v="26400"/>
+    <n v="953.625"/>
+    <n v="3513"/>
+    <n v="22887"/>
+    <n v="1"/>
+    <s v="ECO MARIN 26012N"/>
+    <s v="LIMG03933500"/>
+    <s v="ONE LINE"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="27171.949078027872"/>
+    <n v="9828.4918851710263"/>
+    <n v="325.6303974476296"/>
+    <n v="7313.9286393534703"/>
+    <n v="44640"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-18240"/>
+    <n v="-0.69090909090909092"/>
+    <n v="3513"/>
+    <n v="1384.6153846153848"/>
+    <n v="4897.6153846153848"/>
+    <n v="848.80941035138653"/>
+    <n v="686.61"/>
+    <n v="-23299.814794966769"/>
+    <n v="-0.88256874223358972"/>
+    <n v="1269.6103313645008"/>
+    <n v="-24569.425126331269"/>
+    <n v="-0.93066004266406321"/>
+    <n v="1483.443988387226"/>
+    <n v="-21816.370806579544"/>
+    <n v="-0.82637768206740692"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="179-2026B3"/>
+    <d v="1900-02-22T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="24"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="500-up"/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="1"/>
+    <s v="Julieta"/>
+    <n v="1100"/>
+    <n v="26400"/>
+    <n v="953.625"/>
+    <n v="3513"/>
+    <n v="22887"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <s v="LIMG03937900"/>
+    <s v="ONE LINE"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="27171.949078027872"/>
+    <n v="9828.4918851710263"/>
+    <n v="325.6303974476296"/>
+    <n v="7313.9286393534703"/>
+    <n v="44640"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-18240"/>
+    <n v="-0.69090909090909092"/>
+    <n v="3513"/>
+    <n v="1384.6153846153848"/>
+    <n v="4897.6153846153848"/>
+    <n v="848.80941035138653"/>
+    <n v="686.61"/>
+    <n v="-23299.814794966769"/>
+    <n v="-0.88256874223358972"/>
+    <n v="1269.6103313645008"/>
+    <n v="-24569.425126331269"/>
+    <n v="-0.93066004266406321"/>
+    <n v="1483.443988387226"/>
+    <n v="-21816.370806579544"/>
+    <n v="-0.82637768206740692"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="179-2026B4"/>
+    <d v="1900-02-22T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="24"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="500-up"/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="1"/>
+    <s v="Julieta"/>
+    <n v="1100"/>
+    <n v="26400"/>
+    <n v="953.625"/>
+    <n v="3513"/>
+    <n v="22887"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <s v="LIMG03938300"/>
+    <s v="ONE LINE"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="27171.949078027872"/>
+    <n v="9828.4918851710263"/>
+    <n v="325.6303974476296"/>
+    <n v="7313.9286393534703"/>
+    <n v="44640"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-18240"/>
+    <n v="-0.69090909090909092"/>
+    <n v="3513"/>
+    <n v="1384.6153846153848"/>
+    <n v="4897.6153846153848"/>
+    <n v="848.80941035138653"/>
+    <n v="686.61"/>
+    <n v="-23299.814794966769"/>
+    <n v="-0.88256874223358972"/>
+    <n v="1269.6103313645008"/>
+    <n v="-24569.425126331269"/>
+    <n v="-0.93066004266406321"/>
+    <n v="1483.443988387226"/>
+    <n v="-21816.370806579544"/>
+    <n v="-0.82637768206740692"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="179-2026B5"/>
+    <d v="1900-02-22T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="24"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="500-up"/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="1"/>
+    <s v="Julieta"/>
+    <n v="1100"/>
+    <n v="26400"/>
+    <n v="966.54166666666663"/>
+    <n v="3203"/>
+    <n v="23197"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <s v="LIMG03940300"/>
+    <s v="ONE LINE"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="27171.949078027872"/>
+    <n v="9828.4918851710263"/>
+    <n v="325.6303974476296"/>
+    <n v="7313.9286393534703"/>
+    <n v="44640"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-18240"/>
+    <n v="-0.69090909090909092"/>
+    <n v="3203"/>
+    <n v="1384.6153846153848"/>
+    <n v="4587.6153846153848"/>
+    <n v="848.80941035138653"/>
+    <n v="695.91"/>
+    <n v="-22980.51479496677"/>
+    <n v="-0.87047404526389283"/>
+    <n v="1269.6103313645008"/>
+    <n v="-24250.12512633127"/>
+    <n v="-0.91856534569436632"/>
+    <n v="1483.443988387226"/>
+    <n v="-21497.070806579544"/>
+    <n v="-0.81428298509771002"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="179-2026C1"/>
+    <d v="1900-02-22T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="24"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="1-2 KG "/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="1"/>
+    <s v="KHUNRUNG"/>
+    <n v="1200"/>
+    <n v="28800"/>
+    <n v="1054.1666666666667"/>
+    <n v="3500"/>
+    <n v="25300"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <n v="6447908140"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="27171.949078027872"/>
+    <n v="9828.4918851710263"/>
+    <n v="325.6303974476296"/>
+    <n v="7313.9286393534703"/>
+    <n v="44640"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-15840"/>
+    <n v="-0.55000000000000004"/>
+    <n v="3500"/>
+    <n v="1384.6153846153848"/>
+    <n v="4884.6153846153848"/>
+    <n v="848.80941035138653"/>
+    <n v="759"/>
+    <n v="-20814.42479496677"/>
+    <n v="-0.72272308315856837"/>
+    <n v="1269.6103313645008"/>
+    <n v="-22084.03512633127"/>
+    <n v="-0.76680677521983576"/>
+    <n v="1483.443988387226"/>
+    <n v="-19330.980806579544"/>
+    <n v="-0.6712146113395675"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="179-2026C2"/>
+    <d v="1900-02-22T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="24"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="1-2 KG "/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="1"/>
+    <s v="KHUNRUNG"/>
+    <n v="1200"/>
+    <n v="28800"/>
+    <n v="1054.1666666666667"/>
+    <n v="3500"/>
+    <n v="25300"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <n v="6447908120"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="27171.949078027872"/>
+    <n v="9828.4918851710263"/>
+    <n v="325.6303974476296"/>
+    <n v="7313.9286393534703"/>
+    <n v="44640"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-15840"/>
+    <n v="-0.55000000000000004"/>
+    <n v="3500"/>
+    <n v="1384.6153846153848"/>
+    <n v="4884.6153846153848"/>
+    <n v="848.80941035138653"/>
+    <n v="759"/>
+    <n v="-20814.42479496677"/>
+    <n v="-0.72272308315856837"/>
+    <n v="1269.6103313645008"/>
+    <n v="-22084.03512633127"/>
+    <n v="-0.76680677521983576"/>
+    <n v="1483.443988387226"/>
+    <n v="-19330.980806579544"/>
+    <n v="-0.6712146113395675"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="181-2026"/>
+    <d v="2026-02-24T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="48"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="500-1000"/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="2"/>
+    <s v="Jose"/>
+    <n v="1200"/>
+    <n v="57600"/>
+    <n v="1126.8125"/>
+    <n v="3513"/>
+    <n v="54087"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <s v="LIMG04324700"/>
+    <s v="ONE LINE"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="54343.898156055744"/>
+    <n v="19656.983770342053"/>
+    <n v="651.26079489525921"/>
+    <n v="14627.857278706941"/>
+    <n v="89280"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-31680"/>
+    <n v="-0.55000000000000004"/>
+    <n v="3513"/>
+    <n v="2769.2307692307695"/>
+    <n v="6282.2307692307695"/>
+    <n v="1697.6188207027731"/>
+    <n v="1622.61"/>
+    <n v="-38037.239589933539"/>
+    <n v="-0.66036874288079062"/>
+    <n v="2539.2206627290016"/>
+    <n v="-40576.460252662539"/>
+    <n v="-0.704452434942058"/>
+    <n v="2966.887976774452"/>
+    <n v="-35070.351613159088"/>
+    <n v="-0.60886027106178975"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="183-2026"/>
+    <d v="1900-02-26T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="27"/>
+    <x v="2"/>
+    <s v="Rejos"/>
+    <s v="2- UP LIMPIOS "/>
+    <s v="China "/>
+    <s v="Yantai"/>
+    <x v="14"/>
+    <m/>
+    <n v="2600"/>
+    <n v="70200"/>
+    <n v="2485.1851851851852"/>
+    <n v="3100"/>
+    <n v="67100"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <n v="6447908790"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10007162"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10007162Inventario final"/>
+    <n v="1720"/>
+    <n v="29153.437023253089"/>
+    <n v="8318.700202545584"/>
+    <n v="433.11121745291103"/>
+    <n v="8534.7515567484133"/>
+    <n v="46440"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="23760"/>
+    <n v="0.33846153846153848"/>
+    <n v="3100"/>
+    <n v="1557.6923076923076"/>
+    <n v="4657.6923076923076"/>
+    <n v="954.91058664530988"/>
+    <n v="2013"/>
+    <n v="20160.397105662381"/>
+    <n v="0.28718514395530459"/>
+    <n v="1428.3116227850635"/>
+    <n v="18732.085482877319"/>
+    <n v="0.26683882454241198"/>
+    <n v="1668.8744869356292"/>
+    <n v="21829.271592598012"/>
+    <n v="0.3109582847948435"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="184-2026"/>
+    <d v="1900-02-27T00:00:00"/>
+    <d v="2026-03-23T00:00:00"/>
+    <n v="216"/>
+    <x v="9"/>
+    <s v="Daruma"/>
+    <m/>
+    <s v="China"/>
+    <s v="Qingdao"/>
+    <x v="15"/>
+    <s v="James"/>
+    <n v="3100"/>
+    <n v="669600"/>
+    <n v="2992.5925925925926"/>
+    <n v="23200"/>
+    <n v="646400"/>
+    <n v="8"/>
+    <s v="ECO MARIN 26012N"/>
+    <n v="6447338820"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10009239"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10009239Inventario final"/>
+    <n v="2110"/>
+    <n v="231844.88712129934"/>
+    <n v="151457.49655569636"/>
+    <n v="2915.1833890104826"/>
+    <n v="69542.432933993783"/>
+    <n v="455760"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="213840"/>
+    <n v="0.3193548387096774"/>
+    <n v="23200"/>
+    <n v="12461.538461538461"/>
+    <n v="35661.538461538461"/>
+    <n v="7639.284693162479"/>
+    <n v="19392"/>
+    <n v="189931.17684529905"/>
+    <n v="0.28364871093981342"/>
+    <n v="11426.492982280508"/>
+    <n v="178504.68386301855"/>
+    <n v="0.26658405594835505"/>
+    <n v="13350.995895485034"/>
+    <n v="203282.1727407841"/>
+    <n v="0.30358747422458798"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="185-2026"/>
+    <d v="1900-02-27T00:00:00"/>
+    <d v="2026-03-23T00:00:00"/>
+    <n v="108"/>
+    <x v="9"/>
+    <s v="Daruma "/>
+    <m/>
+    <s v="China "/>
+    <s v="Qingdao"/>
+    <x v="16"/>
+    <s v="James"/>
+    <n v="3100"/>
+    <n v="334800"/>
+    <n v="2992.5925925925926"/>
+    <n v="11600"/>
+    <n v="323200"/>
+    <n v="4"/>
+    <s v="ECO MARIN 26012N"/>
+    <n v="6447338860"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10009239"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10009239Inventario final"/>
+    <n v="2110"/>
+    <n v="115922.44356064967"/>
+    <n v="75728.748277848179"/>
+    <n v="1457.5916945052413"/>
+    <n v="34771.216466996892"/>
+    <n v="227880"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="106920"/>
+    <n v="0.3193548387096774"/>
+    <n v="11600"/>
+    <n v="6230.7692307692305"/>
+    <n v="17830.76923076923"/>
+    <n v="3819.6423465812395"/>
+    <n v="9696"/>
+    <n v="94965.588422649525"/>
+    <n v="0.28364871093981342"/>
+    <n v="5713.246491140254"/>
+    <n v="89252.341931509276"/>
+    <n v="0.26658405594835505"/>
+    <n v="6675.4979477425168"/>
+    <n v="101641.08637039205"/>
+    <n v="0.30358747422458798"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="189-2026"/>
+    <d v="1900-03-08T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="300-500"/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="1"/>
+    <s v="Julieta"/>
+    <n v="1130"/>
+    <n v="11300"/>
+    <n v="990"/>
+    <n v="1400"/>
+    <n v="9900"/>
+    <n v="1"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <n v="6447908000"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="11321.645449178281"/>
+    <n v="4095.2049521545941"/>
+    <n v="135.67933226984567"/>
+    <n v="3047.4702663972794"/>
+    <n v="18600"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-7300"/>
+    <n v="-0.64601769911504425"/>
+    <n v="1400"/>
+    <n v="576.92307692307691"/>
+    <n v="1976.9230769230769"/>
+    <n v="353.67058764641109"/>
+    <n v="297"/>
+    <n v="-9333.5936645694874"/>
+    <n v="-0.82598174022738824"/>
+    <n v="529.00430473520873"/>
+    <n v="-9862.5979693046957"/>
+    <n v="-0.87279628046944213"/>
+    <n v="618.10166182801083"/>
+    <n v="-8715.4920027414773"/>
+    <n v="-0.77128247811871475"/>
+  </r>
+  <r>
+    <s v="FEBRERO"/>
+    <s v="MARZO"/>
+    <s v="189-2026"/>
+    <d v="1900-03-08T00:00:00"/>
+    <d v="2026-03-27T00:00:00"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Nucas"/>
+    <s v="500-1000"/>
+    <s v="Tailandia "/>
+    <s v="Lat Krabang"/>
+    <x v="1"/>
+    <s v="Julieta"/>
+    <n v="1200"/>
+    <n v="18000"/>
+    <n v="1060"/>
+    <n v="2100"/>
+    <n v="15900"/>
+    <n v="0"/>
+    <s v="ECO SIROCCO 26013S"/>
+    <n v="6447908000"/>
+    <s v="COSCO"/>
+    <s v="PAITA"/>
+    <n v="10005779"/>
+    <s v="Inventario final"/>
+    <s v="FEBRERO10005779Inventario final"/>
+    <n v="1860"/>
+    <n v="16982.468173767422"/>
+    <n v="6142.8074282318912"/>
+    <n v="203.51899840476852"/>
+    <n v="4571.2053995959195"/>
+    <n v="27900"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-9900"/>
+    <n v="-0.55000000000000004"/>
+    <n v="2100"/>
+    <n v="865.38461538461536"/>
+    <n v="2965.3846153846152"/>
+    <n v="530.50588146961661"/>
+    <n v="477"/>
+    <n v="-12918.890496854232"/>
+    <n v="-0.71771613871412399"/>
+    <n v="793.5064571028131"/>
+    <n v="-13712.396953957044"/>
+    <n v="-0.76179983077539137"/>
+    <n v="927.15249274201619"/>
+    <n v="-11991.738004112216"/>
+    <n v="-0.66620766689512312"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5DF2661D-96F5-4A44-8024-092F4D4155B5}" name="TablaDinámica7" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5DF2661D-96F5-4A44-8024-092F4D4155B5}" name="TablaDinámica7" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A27:E40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="49">
     <pivotField showAll="0"/>
@@ -6058,7 +9692,825 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD147C22-562A-4E36-A934-5F49E1A2DFA9}" name="TablaDinámica5" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C3A685CA-DBAC-4679-8E3E-1E083D6FE6E1}" name="TablaDinámica1" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A77:E83" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="49">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="8"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item m="1" x="11"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="20">
+        <item x="2"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="15"/>
+        <item x="6"/>
+        <item x="16"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item m="1" x="17"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item m="1" x="18"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="11" item="0" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Suma de VALOR _x000a_FOB" fld="17" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="23">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C6DC3C1-2590-4DE5-81A2-971FF48E579A}" name="TablaDinámica9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C15" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="50">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="12">
+        <item x="8"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="18">
+        <item x="9"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="15"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="4"/>
+        <item x="10"/>
+        <item x="14"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Suma de  Cantidad " fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Suma de VALOR _x000a_CFR" fld="14" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7DD6389-4A9E-4750-BD01-757E12FCA81C}" name="TablaDinámica4" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A49:E68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="49">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="2"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="15"/>
+        <item x="6"/>
+        <item x="16"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item m="1" x="17"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item m="1" x="18"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="18">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de VALOR _x000a_CFR" fld="14" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E86D7460-1F95-46AF-9D20-4ECD924C389E}" name="TablaDinámica9" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="O27:S40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="49">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item m="1" x="11"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de EBITDA" fld="48" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="2">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5C476FD1-E8FD-43C5-AE4A-1756D96C7A11}" name="TablaDinámica8" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H27:L40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="49">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item m="1" x="11"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de UTILIDAD _x000a_NETA" fld="45" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="3">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD147C22-562A-4E36-A934-5F49E1A2DFA9}" name="TablaDinámica5" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H49:L68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="49">
     <pivotField showAll="0"/>
@@ -6221,7 +10673,7 @@
     <dataField name="Suma de UTILIDAD _x000a_NETA" fld="45" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="23">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -6237,9 +10689,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E86D7460-1F95-46AF-9D20-4ECD924C389E}" name="TablaDinámica9" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="O27:S40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB56DA53-F4D0-41B8-9E10-A0D016A5DAB7}" name="TablaDinámica10" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="V49:Z68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="49">
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
@@ -6254,28 +10706,35 @@
     <pivotField numFmtId="16" showAll="0"/>
     <pivotField numFmtId="16" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item m="1" x="11"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="2"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="15"/>
+        <item x="6"/>
+        <item x="16"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item m="1" x="17"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item m="1" x="18"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -6299,7 +10758,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
     <pivotField numFmtId="9" showAll="0"/>
     <pivotField numFmtId="165" showAll="0"/>
     <pivotField numFmtId="165" showAll="0"/>
@@ -6312,12 +10771,12 @@
     <pivotField showAll="0"/>
     <pivotField numFmtId="9" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="6"/>
+    <field x="11"/>
   </rowFields>
-  <rowItems count="12">
+  <rowItems count="18">
     <i>
       <x/>
     </i>
@@ -6349,7 +10808,25 @@
       <x v="9"/>
     </i>
     <i>
+      <x v="10"/>
+    </i>
+    <i>
       <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="18"/>
     </i>
     <i t="grand">
       <x/>
@@ -6373,10 +10850,10 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Suma de EBITDA" fld="48" baseField="0" baseItem="0"/>
+    <dataField name="Suma de UTILIDAD _x000a_BRUTA" fld="35" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="1">
+    <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -6392,8 +10869,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A35569CF-5CC4-4FA3-8F0A-B5B8AA78498B}" name="TablaDinámica6" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A35569CF-5CC4-4FA3-8F0A-B5B8AA78498B}" name="TablaDinámica6" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O49:S68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="49">
     <pivotField showAll="0"/>
@@ -6556,7 +11033,7 @@
     <dataField name="Suma de EBITDA" fld="48" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="2">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -6572,163 +11049,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5C476FD1-E8FD-43C5-AE4A-1756D96C7A11}" name="TablaDinámica8" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="H27:L40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="49">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item m="1" x="11"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de UTILIDAD _x000a_NETA" fld="45" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="3">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D5661A8-232E-4A65-B807-B1C7282237AA}" name="TablaDinámica3" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D5661A8-232E-4A65-B807-B1C7282237AA}" name="TablaDinámica3" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A87:E93" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="49">
     <pivotField showAll="0"/>
@@ -6871,7 +11193,7 @@
     <dataField name="Suma de  Cantidad " fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -6887,348 +11209,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C3A685CA-DBAC-4679-8E3E-1E083D6FE6E1}" name="TablaDinámica1" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A77:E83" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="49">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="8"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item m="1" x="11"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="20">
-        <item x="2"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item x="6"/>
-        <item x="16"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item m="1" x="17"/>
-        <item x="0"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item m="1" x="18"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="11" item="0" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Suma de VALOR _x000a_FOB" fld="17" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="5">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB56DA53-F4D0-41B8-9E10-A0D016A5DAB7}" name="TablaDinámica10" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="V49:Z68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="49">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="2"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item x="6"/>
-        <item x="16"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item m="1" x="17"/>
-        <item x="0"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item m="1" x="18"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="18">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de UTILIDAD _x000a_BRUTA" fld="35" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="6">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2E7087CD-D1D8-4AE8-85E7-EBA4E65796C3}" name="TablaDinámica2" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2E7087CD-D1D8-4AE8-85E7-EBA4E65796C3}" name="TablaDinámica2" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:E18" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="49">
     <pivotField showAll="0"/>
@@ -7361,10 +11343,10 @@
     <dataField name="Suma de EBITDA" fld="48" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="15">
-    <format dxfId="21">
+    <format dxfId="22">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="21">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7373,7 +11355,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7382,7 +11364,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="19">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7391,7 +11373,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7400,7 +11382,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="17">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7409,7 +11391,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7418,7 +11400,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="15">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7427,7 +11409,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7436,7 +11418,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="13">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7445,7 +11427,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7454,7 +11436,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="11">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7463,7 +11445,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7472,7 +11454,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="9">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -7482,7 +11464,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="8">
       <pivotArea field="1" grandCol="1" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7490,186 +11472,6 @@
           </reference>
         </references>
       </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7DD6389-4A9E-4750-BD01-757E12FCA81C}" name="TablaDinámica4" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A49:E68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="49">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="2"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item x="6"/>
-        <item x="16"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item m="1" x="17"/>
-        <item x="0"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item m="1" x="18"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="18">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de VALOR _x000a_CFR" fld="14" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="22">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -42114,4 +45916,162 @@
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0BE130-C52D-4D43-B4CD-F8E9F2A43B6C}">
+  <dimension ref="A3:C15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3">
+      <c r="A3" s="89" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4">
+        <v>1151</v>
+      </c>
+      <c r="C4">
+        <v>1674450</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5">
+        <v>1014.0999999999999</v>
+      </c>
+      <c r="C5">
+        <v>1618945</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>625.76</v>
+      </c>
+      <c r="C6">
+        <v>1554743</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7">
+        <v>419.89</v>
+      </c>
+      <c r="C7">
+        <v>530574</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8">
+        <v>351</v>
+      </c>
+      <c r="C8">
+        <v>1096200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9">
+        <v>105.14</v>
+      </c>
+      <c r="C9">
+        <v>196200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10">
+        <v>77.3</v>
+      </c>
+      <c r="C10">
+        <v>214149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11">
+        <v>54</v>
+      </c>
+      <c r="C11">
+        <v>180900</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12">
+        <v>53.629999999999995</v>
+      </c>
+      <c r="C12">
+        <v>76406.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13">
+        <v>26.63</v>
+      </c>
+      <c r="C13">
+        <v>38606.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>64340.28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15">
+        <v>3878.45</v>
+      </c>
+      <c r="C15">
+        <v>7245513.7800000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/INPUT/Rentabilidad por FP 2026.xlsx
+++ b/INPUT/Rentabilidad por FP 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xitanium\Documents\rodri\xio\xio\Veritrade_Dashboard\INPUT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xitanium\Downloads\INPUT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C55B05-A39E-48C4-B0ED-6BC9DA5CC6D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC9E243-2A68-45ED-BD2C-A7CC73458568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{D0C09B95-B007-4212-AB74-70908523E143}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{D0C09B95-B007-4212-AB74-70908523E143}"/>
   </bookViews>
   <sheets>
     <sheet name="TD" sheetId="3" r:id="rId1"/>
@@ -24,8 +24,8 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="5" r:id="rId5"/>
+    <pivotCache cacheId="6" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -9537,162 +9537,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5DF2661D-96F5-4A44-8024-092F4D4155B5}" name="TablaDinámica7" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A27:E40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="49">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item m="1" x="11"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de VALOR _x000a_CFR" fld="14" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="0">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C3A685CA-DBAC-4679-8E3E-1E083D6FE6E1}" name="TablaDinámica1" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C3A685CA-DBAC-4679-8E3E-1E083D6FE6E1}" name="TablaDinámica1" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A77:E83" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="49">
     <pivotField showAll="0"/>
@@ -9835,6 +9680,161 @@
     <dataField name="Suma de VALOR _x000a_FOB" fld="17" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5C476FD1-E8FD-43C5-AE4A-1756D96C7A11}" name="TablaDinámica8" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H27:L40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="49">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item m="1" x="11"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de UTILIDAD _x000a_NETA" fld="45" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
     <format dxfId="23">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
@@ -9852,7 +9852,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C6DC3C1-2590-4DE5-81A2-971FF48E579A}" name="TablaDinámica9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C6DC3C1-2590-4DE5-81A2-971FF48E579A}" name="TablaDinámica9" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C15" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="50">
     <pivotField showAll="0"/>
@@ -10020,7 +10020,522 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7DD6389-4A9E-4750-BD01-757E12FCA81C}" name="TablaDinámica4" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD147C22-562A-4E36-A934-5F49E1A2DFA9}" name="TablaDinámica5" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H49:L68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="49">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="2"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="15"/>
+        <item x="6"/>
+        <item x="16"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item m="1" x="17"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item m="1" x="18"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="18">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de UTILIDAD _x000a_NETA" fld="45" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB56DA53-F4D0-41B8-9E10-A0D016A5DAB7}" name="TablaDinámica10" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="V49:Z68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="49">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="2"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="15"/>
+        <item x="6"/>
+        <item x="16"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item m="1" x="17"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item m="1" x="18"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="18">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de UTILIDAD _x000a_BRUTA" fld="35" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="2">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5DF2661D-96F5-4A44-8024-092F4D4155B5}" name="TablaDinámica7" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A27:E40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="49">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item m="1" x="11"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de VALOR _x000a_CFR" fld="14" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="3">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7DD6389-4A9E-4750-BD01-757E12FCA81C}" name="TablaDinámica4" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A49:E68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="49">
     <pivotField showAll="0"/>
@@ -10183,496 +10698,6 @@
     <dataField name="Suma de VALOR _x000a_CFR" fld="14" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="1">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E86D7460-1F95-46AF-9D20-4ECD924C389E}" name="TablaDinámica9" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="O27:S40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="49">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item m="1" x="11"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de EBITDA" fld="48" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="2">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5C476FD1-E8FD-43C5-AE4A-1756D96C7A11}" name="TablaDinámica8" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="H27:L40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="49">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item m="1" x="11"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de UTILIDAD _x000a_NETA" fld="45" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="3">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD147C22-562A-4E36-A934-5F49E1A2DFA9}" name="TablaDinámica5" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="H49:L68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="49">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="2"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item x="6"/>
-        <item x="16"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item m="1" x="17"/>
-        <item x="0"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item m="1" x="18"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="18">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de UTILIDAD _x000a_NETA" fld="45" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
     <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
@@ -10690,187 +10715,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB56DA53-F4D0-41B8-9E10-A0D016A5DAB7}" name="TablaDinámica10" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="V49:Z68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="49">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField numFmtId="16" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="2"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item x="6"/>
-        <item x="16"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item m="1" x="17"/>
-        <item x="0"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item m="1" x="18"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="18">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de UTILIDAD _x000a_BRUTA" fld="35" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="5">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A35569CF-5CC4-4FA3-8F0A-B5B8AA78498B}" name="TablaDinámica6" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A35569CF-5CC4-4FA3-8F0A-B5B8AA78498B}" name="TablaDinámica6" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O49:S68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="49">
     <pivotField showAll="0"/>
@@ -11033,6 +10878,161 @@
     <dataField name="Suma de EBITDA" fld="48" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
+    <format dxfId="5">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E86D7460-1F95-46AF-9D20-4ECD924C389E}" name="TablaDinámica9" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="O27:S40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="49">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item m="1" x="11"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de EBITDA" fld="48" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
     <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
@@ -11050,7 +11050,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D5661A8-232E-4A65-B807-B1C7282237AA}" name="TablaDinámica3" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D5661A8-232E-4A65-B807-B1C7282237AA}" name="TablaDinámica3" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A87:E93" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="49">
     <pivotField showAll="0"/>
@@ -11210,7 +11210,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2E7087CD-D1D8-4AE8-85E7-EBA4E65796C3}" name="TablaDinámica2" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2E7087CD-D1D8-4AE8-85E7-EBA4E65796C3}" name="TablaDinámica2" cacheId="5" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:E18" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="49">
     <pivotField showAll="0"/>
